--- a/app/templates/Template_Humedad.xlsx
+++ b/app/templates/Template_Humedad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A034F559-0BB7-4406-90F7-ABFE78422585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169CA48A-6E25-42AE-A137-04A569EE6BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,10 +274,10 @@
     <t xml:space="preserve">Descripción material excluido: </t>
   </si>
   <si>
-    <t>Versión: 05 (16-02-2026)</t>
-  </si>
-  <si>
     <t>Masa del agua (3-5)</t>
+  </si>
+  <si>
+    <t>Versión: 05 (23-02-2026)</t>
   </si>
 </sst>
 </file>
@@ -1044,103 +1044,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1149,6 +1054,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1189,14 +1098,105 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2117,36 +2117,36 @@
       <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="131" t="s">
+      <c r="A7" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
     </row>
     <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132" t="s">
+      <c r="A8" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
     </row>
     <row r="9" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27"/>
@@ -2223,37 +2223,37 @@
       <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="133" t="s">
+      <c r="A14" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="135"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="133"/>
       <c r="M14" s="32"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="143" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="127"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="145"/>
       <c r="M15" s="32"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2272,17 +2272,17 @@
       <c r="M16" s="32"/>
     </row>
     <row r="17" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="136" t="s">
+      <c r="A17" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
       <c r="J17" s="37"/>
       <c r="K17" s="37"/>
       <c r="L17" s="38"/>
@@ -2382,12 +2382,12 @@
       <c r="L23" s="38"/>
     </row>
     <row r="24" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="139"/>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
       <c r="E24" s="100"/>
       <c r="F24" s="100"/>
       <c r="G24" s="100"/>
@@ -2398,56 +2398,56 @@
       <c r="L24" s="38"/>
     </row>
     <row r="25" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="129" t="s">
+      <c r="A25" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="129"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="130" t="s">
+      <c r="B25" s="147"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="130"/>
+      <c r="F25" s="148"/>
       <c r="G25" s="102"/>
-      <c r="H25" s="121" t="s">
+      <c r="H25" s="139" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="122"/>
-      <c r="J25" s="123"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="141"/>
       <c r="K25" s="45"/>
       <c r="L25" s="38"/>
     </row>
     <row r="26" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129" t="s">
+      <c r="A26" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="129"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="130" t="s">
+      <c r="B26" s="147"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="130"/>
+      <c r="F26" s="148"/>
       <c r="G26" s="102"/>
-      <c r="H26" s="124" t="s">
+      <c r="H26" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="124"/>
+      <c r="I26" s="142"/>
       <c r="J26" s="103"/>
       <c r="K26" s="46"/>
       <c r="L26" s="38"/>
     </row>
     <row r="27" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="129" t="s">
+      <c r="A27" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="129"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="130" t="s">
+      <c r="B27" s="147"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="130"/>
+      <c r="F27" s="148"/>
       <c r="G27" s="102"/>
       <c r="H27" s="104"/>
       <c r="I27" s="105"/>
@@ -2457,14 +2457,14 @@
       <c r="M27" s="32"/>
     </row>
     <row r="28" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="129" t="s">
+      <c r="A28" s="147" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="129"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
+      <c r="B28" s="147"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
       <c r="G28" s="107"/>
       <c r="H28" s="107"/>
       <c r="I28" s="107"/>
@@ -2489,22 +2489,22 @@
     </row>
     <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53"/>
-      <c r="B30" s="120" t="s">
+      <c r="B30" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="120"/>
-      <c r="D30" s="120"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
       <c r="H30" s="54" t="s">
         <v>40</v>
       </c>
       <c r="I30" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="146"/>
       <c r="L30" s="55"/>
       <c r="M30" s="32"/>
     </row>
@@ -2513,17 +2513,17 @@
       <c r="B31" s="57">
         <v>1</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C31" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="117"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="152"/>
       <c r="H31" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="154"/>
+      <c r="I31" s="112"/>
       <c r="J31" s="59"/>
       <c r="K31" s="59"/>
       <c r="L31" s="60"/>
@@ -2534,17 +2534,17 @@
       <c r="B32" s="61">
         <v>2</v>
       </c>
-      <c r="C32" s="115" t="s">
+      <c r="C32" s="150" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="116"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="117"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="152"/>
       <c r="H32" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="154"/>
+      <c r="I32" s="112"/>
       <c r="J32" s="59"/>
       <c r="K32" s="59"/>
       <c r="L32" s="60"/>
@@ -2556,17 +2556,17 @@
       <c r="B33" s="61">
         <v>3</v>
       </c>
-      <c r="C33" s="115" t="s">
+      <c r="C33" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="117"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I33" s="154"/>
+      <c r="I33" s="112"/>
       <c r="J33" s="59"/>
       <c r="K33" s="59"/>
       <c r="L33" s="64"/>
@@ -2578,17 +2578,17 @@
       <c r="B34" s="57">
         <v>4</v>
       </c>
-      <c r="C34" s="115" t="s">
+      <c r="C34" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="117"/>
+      <c r="D34" s="151"/>
+      <c r="E34" s="151"/>
+      <c r="F34" s="151"/>
+      <c r="G34" s="152"/>
       <c r="H34" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I34" s="154"/>
+      <c r="I34" s="112"/>
       <c r="J34" s="59"/>
       <c r="K34" s="59"/>
       <c r="L34" s="64"/>
@@ -2602,17 +2602,17 @@
       <c r="B35" s="61">
         <v>5</v>
       </c>
-      <c r="C35" s="115" t="s">
+      <c r="C35" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="117"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I35" s="154"/>
+      <c r="I35" s="112"/>
       <c r="J35" s="59"/>
       <c r="K35" s="59"/>
       <c r="L35" s="66"/>
@@ -2626,17 +2626,17 @@
       <c r="B36" s="57">
         <v>6</v>
       </c>
-      <c r="C36" s="115" t="s">
+      <c r="C36" s="150" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="116"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="117"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="152"/>
       <c r="H36" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I36" s="154"/>
+      <c r="I36" s="112"/>
       <c r="J36" s="59"/>
       <c r="K36" s="59"/>
       <c r="L36" s="66"/>
@@ -2650,17 +2650,17 @@
       <c r="B37" s="61">
         <v>7</v>
       </c>
-      <c r="C37" s="115" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="117"/>
+      <c r="C37" s="150" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="152"/>
       <c r="H37" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="154"/>
+      <c r="I37" s="112"/>
       <c r="J37" s="59"/>
       <c r="K37" s="59"/>
       <c r="L37" s="66"/>
@@ -2674,17 +2674,17 @@
       <c r="B38" s="61">
         <v>8</v>
       </c>
-      <c r="C38" s="115" t="s">
+      <c r="C38" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="117"/>
+      <c r="D38" s="151"/>
+      <c r="E38" s="151"/>
+      <c r="F38" s="151"/>
+      <c r="G38" s="152"/>
       <c r="H38" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="154"/>
+      <c r="I38" s="112"/>
       <c r="J38" s="59"/>
       <c r="K38" s="59"/>
       <c r="L38" s="66"/>
@@ -2698,17 +2698,17 @@
       <c r="B39" s="57">
         <v>9</v>
       </c>
-      <c r="C39" s="115" t="s">
+      <c r="C39" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="116"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="117"/>
+      <c r="D39" s="151"/>
+      <c r="E39" s="151"/>
+      <c r="F39" s="151"/>
+      <c r="G39" s="152"/>
       <c r="H39" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I39" s="154"/>
+      <c r="I39" s="112"/>
       <c r="J39" s="59"/>
       <c r="K39" s="59"/>
       <c r="L39" s="66"/>
@@ -2734,31 +2734,31 @@
     </row>
     <row r="41" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56"/>
-      <c r="B41" s="118" t="s">
+      <c r="B41" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
+      <c r="C41" s="126"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
+      <c r="F41" s="126"/>
       <c r="G41" s="74"/>
-      <c r="H41" s="142" t="s">
+      <c r="H41" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="I41" s="113"/>
-      <c r="J41" s="112"/>
-      <c r="K41" s="112"/>
-      <c r="L41" s="113"/>
+      <c r="I41" s="116"/>
+      <c r="J41" s="149"/>
+      <c r="K41" s="149"/>
+      <c r="L41" s="116"/>
       <c r="M41" s="32"/>
       <c r="W41" s="63"/>
     </row>
     <row r="42" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56"/>
-      <c r="B42" s="152" t="s">
+      <c r="B42" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="152"/>
-      <c r="D42" s="152"/>
+      <c r="C42" s="127"/>
+      <c r="D42" s="127"/>
       <c r="E42" s="75" t="s">
         <v>48</v>
       </c>
@@ -2766,23 +2766,23 @@
         <v>62</v>
       </c>
       <c r="G42" s="74"/>
-      <c r="H42" s="151" t="s">
+      <c r="H42" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="151"/>
-      <c r="J42" s="150"/>
-      <c r="K42" s="150"/>
-      <c r="L42" s="150"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="124"/>
+      <c r="K42" s="124"/>
+      <c r="L42" s="124"/>
       <c r="M42" s="32"/>
       <c r="W42" s="63"/>
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56"/>
-      <c r="B43" s="114" t="s">
+      <c r="B43" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="114"/>
-      <c r="D43" s="114"/>
+      <c r="C43" s="128"/>
+      <c r="D43" s="128"/>
       <c r="E43" s="76" t="s">
         <v>23</v>
       </c>
@@ -2790,23 +2790,23 @@
         <v>63</v>
       </c>
       <c r="G43" s="74"/>
-      <c r="H43" s="151" t="s">
+      <c r="H43" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="151"/>
-      <c r="J43" s="143"/>
-      <c r="K43" s="143"/>
-      <c r="L43" s="144"/>
+      <c r="I43" s="125"/>
+      <c r="J43" s="117"/>
+      <c r="K43" s="117"/>
+      <c r="L43" s="118"/>
       <c r="M43" s="32"/>
       <c r="W43" s="63"/>
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56"/>
-      <c r="B44" s="114" t="s">
+      <c r="B44" s="128" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="114"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="128"/>
+      <c r="D44" s="128"/>
       <c r="E44" s="76" t="s">
         <v>22</v>
       </c>
@@ -2814,20 +2814,20 @@
         <v>63</v>
       </c>
       <c r="G44" s="74"/>
-      <c r="H44" s="151"/>
-      <c r="I44" s="151"/>
-      <c r="J44" s="145"/>
-      <c r="K44" s="145"/>
-      <c r="L44" s="146"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="125"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="120"/>
       <c r="M44" s="32"/>
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56"/>
-      <c r="B45" s="119" t="s">
+      <c r="B45" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="119"/>
-      <c r="D45" s="119"/>
+      <c r="C45" s="153"/>
+      <c r="D45" s="153"/>
       <c r="E45" s="76" t="s">
         <v>21</v>
       </c>
@@ -2835,39 +2835,39 @@
         <v>63</v>
       </c>
       <c r="G45" s="74"/>
-      <c r="H45" s="151" t="s">
+      <c r="H45" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="151"/>
-      <c r="J45" s="143"/>
-      <c r="K45" s="143"/>
-      <c r="L45" s="144"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="117"/>
+      <c r="K45" s="117"/>
+      <c r="L45" s="118"/>
       <c r="M45" s="32"/>
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56"/>
-      <c r="B46" s="118" t="s">
+      <c r="B46" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="118"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="118"/>
+      <c r="C46" s="126"/>
+      <c r="D46" s="126"/>
+      <c r="E46" s="126"/>
+      <c r="F46" s="126"/>
       <c r="G46" s="74"/>
-      <c r="H46" s="151"/>
-      <c r="I46" s="151"/>
-      <c r="J46" s="145"/>
-      <c r="K46" s="145"/>
-      <c r="L46" s="146"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="119"/>
+      <c r="K46" s="119"/>
+      <c r="L46" s="120"/>
       <c r="M46" s="32"/>
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="56"/>
-      <c r="B47" s="119" t="s">
+      <c r="B47" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="153"/>
       <c r="E47" s="76" t="s">
         <v>20</v>
       </c>
@@ -2875,20 +2875,20 @@
         <v>64</v>
       </c>
       <c r="G47" s="74"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="148"/>
-      <c r="K47" s="148"/>
-      <c r="L47" s="149"/>
+      <c r="H47" s="121"/>
+      <c r="I47" s="121"/>
+      <c r="J47" s="122"/>
+      <c r="K47" s="122"/>
+      <c r="L47" s="123"/>
       <c r="M47" s="32"/>
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="56"/>
-      <c r="B48" s="114" t="s">
+      <c r="B48" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
+      <c r="C48" s="128"/>
+      <c r="D48" s="128"/>
       <c r="E48" s="76" t="s">
         <v>21</v>
       </c>
@@ -2896,20 +2896,20 @@
         <v>64</v>
       </c>
       <c r="G48" s="74"/>
-      <c r="H48" s="147"/>
-      <c r="I48" s="147"/>
-      <c r="J48" s="148"/>
-      <c r="K48" s="148"/>
-      <c r="L48" s="149"/>
+      <c r="H48" s="121"/>
+      <c r="I48" s="121"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="123"/>
       <c r="M48" s="32"/>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="56"/>
-      <c r="B49" s="114" t="s">
+      <c r="B49" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="114"/>
-      <c r="D49" s="114"/>
+      <c r="C49" s="128"/>
+      <c r="D49" s="128"/>
       <c r="E49" s="76" t="s">
         <v>21</v>
       </c>
@@ -3027,15 +3027,15 @@
       <c r="M56" s="32"/>
     </row>
     <row r="57" spans="1:13" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="141"/>
-      <c r="C57" s="141"/>
-      <c r="D57" s="141"/>
-      <c r="E57" s="141"/>
-      <c r="F57" s="141"/>
-      <c r="G57" s="141"/>
-      <c r="H57" s="141"/>
-      <c r="I57" s="141"/>
-      <c r="J57" s="141"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="114"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
       <c r="K57" s="29"/>
       <c r="L57" s="63"/>
       <c r="M57" s="32"/>
@@ -3059,7 +3059,7 @@
     </row>
     <row r="59" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B59" s="63"/>
       <c r="C59" s="63"/>
@@ -3078,20 +3078,20 @@
     </row>
     <row r="60" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="140" t="s">
+      <c r="A61" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="140"/>
-      <c r="C61" s="140"/>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
-      <c r="F61" s="140"/>
-      <c r="G61" s="140"/>
-      <c r="H61" s="140"/>
-      <c r="I61" s="140"/>
-      <c r="J61" s="140"/>
-      <c r="K61" s="140"/>
-      <c r="L61" s="140"/>
+      <c r="B61" s="113"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="113"/>
+      <c r="G61" s="113"/>
+      <c r="H61" s="113"/>
+      <c r="I61" s="113"/>
+      <c r="J61" s="113"/>
+      <c r="K61" s="113"/>
+      <c r="L61" s="113"/>
     </row>
     <row r="62" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3101,6 +3101,40 @@
     <protectedRange sqref="C57" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="50">
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="E57:H57"/>
@@ -3117,40 +3151,6 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="H45:I46"/>
     <mergeCell ref="H43:I44"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A18:A22">
@@ -3197,10 +3197,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="153"/>
+      <c r="B2" s="154"/>
       <c r="C2" s="5" t="s">
         <v>10</v>
       </c>

--- a/app/templates/Template_Humedad.xlsx
+++ b/app/templates/Template_Humedad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\modules\informe_complet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1544522D-B608-468B-A0E5-8E996B86D80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7E7A1D-B178-4CCF-B6A2-07B5D3133E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="348">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -1408,12 +1408,30 @@
     <t>Fecha calibracion</t>
   </si>
   <si>
-    <t>Aprobado:
-Fecha</t>
-  </si>
-  <si>
     <t xml:space="preserve">Revisado:
 Fecha: </t>
+  </si>
+  <si>
+    <t>REVISADO POR:</t>
+  </si>
+  <si>
+    <t>FABIAN LA ROSA</t>
+  </si>
+  <si>
+    <t>APROBADO POR:</t>
+  </si>
+  <si>
+    <t>IRMA COAQUIRA</t>
+  </si>
+  <si>
+    <t>FECHA DE REVISIÓN:</t>
+  </si>
+  <si>
+    <t>FECHA DE APROBACIÓN:</t>
+  </si>
+  <si>
+    <t>Aprobado:
+Fecha:</t>
   </si>
 </sst>
 </file>
@@ -1448,10 +1466,17 @@
     <numFmt numFmtId="188" formatCode="000\-\ &quot;26&quot;"/>
     <numFmt numFmtId="189" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="84">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1959,6 +1984,14 @@
       <u/>
       <sz val="10"/>
       <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2638,353 +2671,356 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="735">
+  <cellXfs count="745">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="175" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="16" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="17" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -2992,11 +3028,11 @@
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -3004,238 +3040,695 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="11" fontId="35" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="36" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="50" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="37" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="37" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="38" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="2" fontId="39" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="52" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="40" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="53" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="54" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="48" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="38" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="175" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="60" fillId="2" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="60" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="31" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="17" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="17" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="17" fillId="11" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="29" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="30" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="12" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="12" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="12" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="18" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="69" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="72" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="72" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3243,1285 +3736,1238 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="72" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="76" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="75" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="39" fillId="11" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="11" fontId="5" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="72" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="69" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="69" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="179" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="59" fillId="2" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="59" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="31" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="16" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="16" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="16" fillId="11" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="29" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="16" fillId="12" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="12" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="12" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="12" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="18" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="12" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="12" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="68" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="71" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="60" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="60" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="80" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="72" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="67" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="72" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="71" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="75" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="74" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="45" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="11" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="11" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="68" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="73" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="68" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="59" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="59" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="12" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="73" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="79" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="12" fontId="71" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="66" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="71" fillId="12" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="189" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="72" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="12" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="186" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="12" fontId="24" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="186" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="23" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -4532,551 +4978,170 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="183" fontId="60" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="189" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="23" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="16" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="72" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="13">
     <cellStyle name="Hipervínculo" xfId="9" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3 2" xfId="11" xr:uid="{3976F643-75BE-4E31-B2AD-9BB35D9DE4CE}"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Normal 6" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Normal 6 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 6 2 2" xfId="12" xr:uid="{377EA88F-E0DA-47E3-BFCB-AB1600DDD727}"/>
+    <cellStyle name="Normal 6 3" xfId="10" xr:uid="{73C8865C-1DB3-4A14-AE86-6CDC0E78EA77}"/>
     <cellStyle name="Normal_ENSAYOS" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Normal_Produc. 07-09-99 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
@@ -7553,35 +7618,35 @@
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="15.9" customHeight="1">
-      <c r="A7" s="491" t="s">
+      <c r="A7" s="572" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="491"/>
-      <c r="C7" s="491"/>
-      <c r="D7" s="491"/>
-      <c r="E7" s="491"/>
-      <c r="F7" s="491"/>
-      <c r="G7" s="491"/>
-      <c r="H7" s="491"/>
-      <c r="I7" s="491"/>
-      <c r="J7" s="491"/>
-      <c r="K7" s="491"/>
+      <c r="B7" s="572"/>
+      <c r="C7" s="572"/>
+      <c r="D7" s="572"/>
+      <c r="E7" s="572"/>
+      <c r="F7" s="572"/>
+      <c r="G7" s="572"/>
+      <c r="H7" s="572"/>
+      <c r="I7" s="572"/>
+      <c r="J7" s="572"/>
+      <c r="K7" s="572"/>
     </row>
     <row r="8" spans="1:18" ht="15.9" customHeight="1">
-      <c r="A8" s="512">
+      <c r="A8" s="593">
         <f>K13</f>
         <v>15</v>
       </c>
-      <c r="B8" s="512"/>
-      <c r="C8" s="512"/>
-      <c r="D8" s="512"/>
-      <c r="E8" s="512"/>
-      <c r="F8" s="512"/>
-      <c r="G8" s="512"/>
-      <c r="H8" s="512"/>
-      <c r="I8" s="512"/>
-      <c r="J8" s="512"/>
-      <c r="K8" s="512"/>
+      <c r="B8" s="593"/>
+      <c r="C8" s="593"/>
+      <c r="D8" s="593"/>
+      <c r="E8" s="593"/>
+      <c r="F8" s="593"/>
+      <c r="G8" s="593"/>
+      <c r="H8" s="593"/>
+      <c r="I8" s="593"/>
+      <c r="J8" s="593"/>
+      <c r="K8" s="593"/>
     </row>
     <row r="9" spans="1:18" ht="15.9" customHeight="1">
       <c r="P9" s="17"/>
@@ -7692,8 +7757,8 @@
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
-      <c r="Q13" s="503"/>
-      <c r="R13" s="503"/>
+      <c r="Q13" s="584"/>
+      <c r="R13" s="584"/>
     </row>
     <row r="14" spans="1:18" ht="15.9" customHeight="1">
       <c r="A14" s="167" t="s">
@@ -7716,19 +7781,19 @@
       <c r="R14" s="321"/>
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1">
-      <c r="A15" s="504" t="s">
+      <c r="A15" s="585" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="505"/>
-      <c r="C15" s="505"/>
-      <c r="D15" s="505"/>
-      <c r="E15" s="505"/>
-      <c r="F15" s="505"/>
-      <c r="G15" s="505"/>
-      <c r="H15" s="505"/>
-      <c r="I15" s="505"/>
-      <c r="J15" s="505"/>
-      <c r="K15" s="506"/>
+      <c r="B15" s="586"/>
+      <c r="C15" s="586"/>
+      <c r="D15" s="586"/>
+      <c r="E15" s="586"/>
+      <c r="F15" s="586"/>
+      <c r="G15" s="586"/>
+      <c r="H15" s="586"/>
+      <c r="I15" s="586"/>
+      <c r="J15" s="586"/>
+      <c r="K15" s="587"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
@@ -7736,19 +7801,19 @@
       <c r="R15" s="321"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1">
-      <c r="A16" s="509" t="s">
+      <c r="A16" s="590" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="510"/>
-      <c r="C16" s="510"/>
-      <c r="D16" s="510"/>
-      <c r="E16" s="510"/>
-      <c r="F16" s="510"/>
-      <c r="G16" s="510"/>
-      <c r="H16" s="510"/>
-      <c r="I16" s="510"/>
-      <c r="J16" s="510"/>
-      <c r="K16" s="511"/>
+      <c r="B16" s="591"/>
+      <c r="C16" s="591"/>
+      <c r="D16" s="591"/>
+      <c r="E16" s="591"/>
+      <c r="F16" s="591"/>
+      <c r="G16" s="591"/>
+      <c r="H16" s="591"/>
+      <c r="I16" s="591"/>
+      <c r="J16" s="591"/>
+      <c r="K16" s="592"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="25"/>
@@ -7756,10 +7821,10 @@
       <c r="R16" s="321"/>
     </row>
     <row r="17" spans="1:26" ht="11.25" customHeight="1">
-      <c r="A17" s="492" t="s">
+      <c r="A17" s="573" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="493"/>
+      <c r="B17" s="574"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -7776,8 +7841,8 @@
       <c r="R17" s="321"/>
     </row>
     <row r="18" spans="1:26" ht="15.9" customHeight="1">
-      <c r="A18" s="494"/>
-      <c r="B18" s="495"/>
+      <c r="A18" s="575"/>
+      <c r="B18" s="576"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
@@ -7922,10 +7987,10 @@
       <c r="P21" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="535">
+      <c r="Q21" s="616">
         <v>44090</v>
       </c>
-      <c r="R21" s="535"/>
+      <c r="R21" s="616"/>
       <c r="S21" s="94"/>
       <c r="T21" s="95"/>
       <c r="U21" s="94"/>
@@ -7968,15 +8033,15 @@
     </row>
     <row r="23" spans="1:26" ht="13.5" customHeight="1" thickBot="1">
       <c r="A23" s="168"/>
-      <c r="B23" s="513"/>
-      <c r="C23" s="513"/>
+      <c r="B23" s="594"/>
+      <c r="C23" s="594"/>
       <c r="D23" s="323"/>
       <c r="E23" s="323"/>
       <c r="F23" s="323"/>
       <c r="G23" s="323"/>
       <c r="H23" s="323"/>
-      <c r="I23" s="513"/>
-      <c r="J23" s="513"/>
+      <c r="I23" s="594"/>
+      <c r="J23" s="594"/>
       <c r="K23" s="168"/>
       <c r="L23" s="25"/>
       <c r="M23" s="49"/>
@@ -7998,8 +8063,8 @@
         <f>+R24</f>
         <v>1</v>
       </c>
-      <c r="I24" s="507"/>
-      <c r="J24" s="507"/>
+      <c r="I24" s="588"/>
+      <c r="J24" s="588"/>
       <c r="K24" s="322"/>
       <c r="L24" s="25"/>
       <c r="M24" s="54"/>
@@ -8013,21 +8078,21 @@
       <c r="R24" s="56">
         <v>1</v>
       </c>
-      <c r="S24" s="496" t="s">
+      <c r="S24" s="577" t="s">
         <v>37</v>
       </c>
       <c r="U24" s="56">
         <v>2</v>
       </c>
-      <c r="V24" s="496" t="s">
+      <c r="V24" s="577" t="s">
         <v>37</v>
       </c>
-      <c r="W24" s="531" t="s">
+      <c r="W24" s="612" t="s">
         <v>38</v>
       </c>
-      <c r="X24" s="531"/>
-      <c r="Y24" s="531"/>
-      <c r="Z24" s="532"/>
+      <c r="X24" s="612"/>
+      <c r="Y24" s="612"/>
+      <c r="Z24" s="613"/>
     </row>
     <row r="25" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A25" s="171"/>
@@ -8045,8 +8110,8 @@
         <f>+R25</f>
         <v>1</v>
       </c>
-      <c r="I25" s="507"/>
-      <c r="J25" s="507"/>
+      <c r="I25" s="588"/>
+      <c r="J25" s="588"/>
       <c r="K25" s="322"/>
       <c r="L25" s="25"/>
       <c r="M25" s="54"/>
@@ -8060,15 +8125,15 @@
       <c r="R25" s="59">
         <v>1</v>
       </c>
-      <c r="S25" s="496"/>
+      <c r="S25" s="577"/>
       <c r="U25" s="59">
         <v>2</v>
       </c>
-      <c r="V25" s="496"/>
-      <c r="W25" s="533"/>
-      <c r="X25" s="533"/>
-      <c r="Y25" s="533"/>
-      <c r="Z25" s="534"/>
+      <c r="V25" s="577"/>
+      <c r="W25" s="614"/>
+      <c r="X25" s="614"/>
+      <c r="Y25" s="614"/>
+      <c r="Z25" s="615"/>
     </row>
     <row r="26" spans="1:26" ht="17.25" customHeight="1">
       <c r="A26" s="171"/>
@@ -8086,8 +8151,8 @@
         <f>S26</f>
         <v>794.6995891401001</v>
       </c>
-      <c r="I26" s="508"/>
-      <c r="J26" s="508"/>
+      <c r="I26" s="589"/>
+      <c r="J26" s="589"/>
       <c r="K26" s="169"/>
       <c r="L26" s="60"/>
       <c r="M26" s="54"/>
@@ -8429,14 +8494,14 @@
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
-      <c r="P34" s="497" t="s">
+      <c r="P34" s="578" t="s">
         <v>59</v>
       </c>
-      <c r="Q34" s="498"/>
-      <c r="R34" s="501" t="s">
+      <c r="Q34" s="579"/>
+      <c r="R34" s="582" t="s">
         <v>60</v>
       </c>
-      <c r="S34" s="501" t="s">
+      <c r="S34" s="582" t="s">
         <v>61</v>
       </c>
       <c r="T34" s="132"/>
@@ -8449,10 +8514,10 @@
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
-      <c r="P35" s="499"/>
-      <c r="Q35" s="500"/>
-      <c r="R35" s="502"/>
-      <c r="S35" s="502"/>
+      <c r="P35" s="580"/>
+      <c r="Q35" s="581"/>
+      <c r="R35" s="583"/>
+      <c r="S35" s="583"/>
       <c r="T35" s="133"/>
       <c r="U35" s="132"/>
       <c r="V35" s="132"/>
@@ -8540,7 +8605,7 @@
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
-      <c r="P38" s="517" t="s">
+      <c r="P38" s="598" t="s">
         <v>72</v>
       </c>
       <c r="Q38" s="108">
@@ -8557,16 +8622,16 @@
       <c r="V38" s="135"/>
     </row>
     <row r="39" spans="1:22" ht="14.25" customHeight="1">
-      <c r="A39" s="514" t="s">
+      <c r="A39" s="595" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="514"/>
-      <c r="C39" s="514"/>
-      <c r="D39" s="514"/>
-      <c r="E39" s="514"/>
-      <c r="F39" s="514"/>
-      <c r="G39" s="514"/>
-      <c r="H39" s="515"/>
+      <c r="B39" s="595"/>
+      <c r="C39" s="595"/>
+      <c r="D39" s="595"/>
+      <c r="E39" s="595"/>
+      <c r="F39" s="595"/>
+      <c r="G39" s="595"/>
+      <c r="H39" s="596"/>
       <c r="I39" s="166" t="s">
         <v>67</v>
       </c>
@@ -8575,7 +8640,7 @@
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
       <c r="N39" s="25"/>
-      <c r="P39" s="518"/>
+      <c r="P39" s="599"/>
       <c r="Q39" s="108">
         <v>0.75</v>
       </c>
@@ -8600,7 +8665,7 @@
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="N40" s="25"/>
-      <c r="P40" s="518"/>
+      <c r="P40" s="599"/>
       <c r="Q40" s="108">
         <v>1.5</v>
       </c>
@@ -8627,7 +8692,7 @@
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
       <c r="N41" s="25"/>
-      <c r="P41" s="519"/>
+      <c r="P41" s="600"/>
       <c r="Q41" s="104">
         <v>3</v>
       </c>
@@ -8758,7 +8823,7 @@
       </c>
       <c r="T45" s="86"/>
       <c r="U45" s="102"/>
-      <c r="V45" s="516"/>
+      <c r="V45" s="597"/>
     </row>
     <row r="46" spans="1:22" ht="15.9" customHeight="1">
       <c r="C46" s="42"/>
@@ -8784,7 +8849,7 @@
       </c>
       <c r="T46" s="86"/>
       <c r="U46" s="106"/>
-      <c r="V46" s="516"/>
+      <c r="V46" s="597"/>
     </row>
     <row r="47" spans="1:22" ht="12.75" customHeight="1">
       <c r="A47" s="154" t="s">
@@ -8873,30 +8938,30 @@
       <c r="V50" s="107"/>
     </row>
     <row r="51" spans="1:22" ht="33" customHeight="1">
-      <c r="A51" s="529" t="s">
+      <c r="A51" s="610" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="529"/>
-      <c r="C51" s="529"/>
-      <c r="D51" s="529"/>
-      <c r="E51" s="529"/>
-      <c r="F51" s="529"/>
-      <c r="G51" s="529"/>
-      <c r="H51" s="529"/>
-      <c r="I51" s="529"/>
-      <c r="J51" s="529"/>
-      <c r="K51" s="529"/>
+      <c r="B51" s="610"/>
+      <c r="C51" s="610"/>
+      <c r="D51" s="610"/>
+      <c r="E51" s="610"/>
+      <c r="F51" s="610"/>
+      <c r="G51" s="610"/>
+      <c r="H51" s="610"/>
+      <c r="I51" s="610"/>
+      <c r="J51" s="610"/>
+      <c r="K51" s="610"/>
       <c r="T51" s="86"/>
       <c r="U51" s="109"/>
       <c r="V51" s="107"/>
     </row>
     <row r="52" spans="1:22" ht="11.25" customHeight="1">
-      <c r="H52" s="528" t="s">
+      <c r="H52" s="609" t="s">
         <v>97</v>
       </c>
-      <c r="I52" s="528"/>
-      <c r="J52" s="528"/>
-      <c r="K52" s="528"/>
+      <c r="I52" s="609"/>
+      <c r="J52" s="609"/>
+      <c r="K52" s="609"/>
       <c r="T52" s="86"/>
       <c r="U52" s="109"/>
       <c r="V52" s="107"/>
@@ -8911,14 +8976,14 @@
     <row r="54" spans="1:22">
       <c r="J54" s="72"/>
       <c r="K54" s="71"/>
-      <c r="T54" s="530"/>
+      <c r="T54" s="611"/>
       <c r="U54" s="109"/>
       <c r="V54" s="107"/>
     </row>
     <row r="55" spans="1:22">
       <c r="J55"/>
       <c r="K55" s="71"/>
-      <c r="T55" s="530"/>
+      <c r="T55" s="611"/>
       <c r="U55" s="109"/>
       <c r="V55" s="107"/>
     </row>
@@ -8958,58 +9023,58 @@
       <c r="K58" s="73"/>
     </row>
     <row r="59" spans="1:22">
-      <c r="A59" s="520" t="s">
+      <c r="A59" s="601" t="s">
         <v>98</v>
       </c>
-      <c r="B59" s="522"/>
-      <c r="C59" s="522"/>
-      <c r="D59" s="522"/>
-      <c r="E59" s="522"/>
-      <c r="F59" s="522"/>
-      <c r="G59" s="522"/>
-      <c r="H59" s="522"/>
-      <c r="I59" s="522"/>
-      <c r="J59" s="522"/>
-      <c r="K59" s="523"/>
+      <c r="B59" s="603"/>
+      <c r="C59" s="603"/>
+      <c r="D59" s="603"/>
+      <c r="E59" s="603"/>
+      <c r="F59" s="603"/>
+      <c r="G59" s="603"/>
+      <c r="H59" s="603"/>
+      <c r="I59" s="603"/>
+      <c r="J59" s="603"/>
+      <c r="K59" s="604"/>
     </row>
     <row r="60" spans="1:22">
-      <c r="A60" s="521"/>
-      <c r="B60" s="524"/>
-      <c r="C60" s="524"/>
-      <c r="D60" s="524"/>
-      <c r="E60" s="524"/>
-      <c r="F60" s="524"/>
-      <c r="G60" s="524"/>
-      <c r="H60" s="524"/>
-      <c r="I60" s="524"/>
-      <c r="J60" s="524"/>
-      <c r="K60" s="525"/>
+      <c r="A60" s="602"/>
+      <c r="B60" s="605"/>
+      <c r="C60" s="605"/>
+      <c r="D60" s="605"/>
+      <c r="E60" s="605"/>
+      <c r="F60" s="605"/>
+      <c r="G60" s="605"/>
+      <c r="H60" s="605"/>
+      <c r="I60" s="605"/>
+      <c r="J60" s="605"/>
+      <c r="K60" s="606"/>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="74"/>
-      <c r="B61" s="524"/>
-      <c r="C61" s="524"/>
-      <c r="D61" s="524"/>
-      <c r="E61" s="524"/>
-      <c r="F61" s="524"/>
-      <c r="G61" s="524"/>
-      <c r="H61" s="524"/>
-      <c r="I61" s="524"/>
-      <c r="J61" s="524"/>
-      <c r="K61" s="525"/>
+      <c r="B61" s="605"/>
+      <c r="C61" s="605"/>
+      <c r="D61" s="605"/>
+      <c r="E61" s="605"/>
+      <c r="F61" s="605"/>
+      <c r="G61" s="605"/>
+      <c r="H61" s="605"/>
+      <c r="I61" s="605"/>
+      <c r="J61" s="605"/>
+      <c r="K61" s="606"/>
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="75"/>
-      <c r="B62" s="526"/>
-      <c r="C62" s="526"/>
-      <c r="D62" s="526"/>
-      <c r="E62" s="526"/>
-      <c r="F62" s="526"/>
-      <c r="G62" s="526"/>
-      <c r="H62" s="526"/>
-      <c r="I62" s="526"/>
-      <c r="J62" s="526"/>
-      <c r="K62" s="527"/>
+      <c r="B62" s="607"/>
+      <c r="C62" s="607"/>
+      <c r="D62" s="607"/>
+      <c r="E62" s="607"/>
+      <c r="F62" s="607"/>
+      <c r="G62" s="607"/>
+      <c r="H62" s="607"/>
+      <c r="I62" s="607"/>
+      <c r="J62" s="607"/>
+      <c r="K62" s="608"/>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="76"/>
@@ -9105,15 +9170,15 @@
       <c r="K85"/>
     </row>
     <row r="86" spans="8:11">
-      <c r="H86" s="516"/>
-      <c r="I86" s="516"/>
-      <c r="J86" s="516"/>
+      <c r="H86" s="597"/>
+      <c r="I86" s="597"/>
+      <c r="J86" s="597"/>
       <c r="K86"/>
     </row>
     <row r="87" spans="8:11">
-      <c r="H87" s="516"/>
-      <c r="I87" s="516"/>
-      <c r="J87" s="516"/>
+      <c r="H87" s="597"/>
+      <c r="I87" s="597"/>
+      <c r="J87" s="597"/>
       <c r="K87"/>
     </row>
     <row r="88" spans="8:11">
@@ -9298,136 +9363,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="12.75" customHeight="1" thickTop="1">
-      <c r="A1" s="618"/>
-      <c r="B1" s="619"/>
-      <c r="C1" s="619"/>
-      <c r="D1" s="620"/>
-      <c r="E1" s="620"/>
-      <c r="F1" s="620"/>
-      <c r="G1" s="620"/>
-      <c r="H1" s="620"/>
-      <c r="I1" s="620"/>
-      <c r="J1" s="621"/>
-      <c r="K1" s="621"/>
-      <c r="L1" s="622"/>
+      <c r="A1" s="491"/>
+      <c r="B1" s="492"/>
+      <c r="C1" s="492"/>
+      <c r="D1" s="493"/>
+      <c r="E1" s="493"/>
+      <c r="F1" s="493"/>
+      <c r="G1" s="493"/>
+      <c r="H1" s="493"/>
+      <c r="I1" s="493"/>
+      <c r="J1" s="494"/>
+      <c r="K1" s="494"/>
+      <c r="L1" s="495"/>
     </row>
     <row r="2" spans="1:16" ht="12.75" customHeight="1">
-      <c r="A2" s="623"/>
-      <c r="B2" s="624"/>
-      <c r="C2" s="624"/>
-      <c r="D2" s="625"/>
-      <c r="E2" s="625"/>
-      <c r="F2" s="625"/>
-      <c r="G2" s="625"/>
-      <c r="H2" s="625"/>
-      <c r="I2" s="625"/>
-      <c r="L2" s="626"/>
+      <c r="A2" s="496"/>
+      <c r="B2" s="497"/>
+      <c r="C2" s="497"/>
+      <c r="D2" s="498"/>
+      <c r="E2" s="498"/>
+      <c r="F2" s="498"/>
+      <c r="G2" s="498"/>
+      <c r="H2" s="498"/>
+      <c r="I2" s="498"/>
+      <c r="L2" s="499"/>
       <c r="O2" s="475" t="s">
         <v>1</v>
       </c>
       <c r="P2" s="476"/>
     </row>
     <row r="3" spans="1:16" ht="12.75" customHeight="1">
-      <c r="A3" s="623"/>
-      <c r="B3" s="624"/>
-      <c r="C3" s="624"/>
-      <c r="D3" s="625"/>
-      <c r="E3" s="625"/>
-      <c r="F3" s="625"/>
-      <c r="G3" s="625"/>
-      <c r="H3" s="625"/>
-      <c r="I3" s="625"/>
-      <c r="L3" s="626"/>
+      <c r="A3" s="496"/>
+      <c r="B3" s="497"/>
+      <c r="C3" s="497"/>
+      <c r="D3" s="498"/>
+      <c r="E3" s="498"/>
+      <c r="F3" s="498"/>
+      <c r="G3" s="498"/>
+      <c r="H3" s="498"/>
+      <c r="I3" s="498"/>
+      <c r="L3" s="499"/>
       <c r="O3" s="475" t="s">
         <v>100</v>
       </c>
       <c r="P3" s="477"/>
     </row>
     <row r="4" spans="1:16" ht="12.75" customHeight="1">
-      <c r="A4" s="623"/>
-      <c r="B4" s="624"/>
-      <c r="C4" s="624"/>
-      <c r="D4" s="625"/>
-      <c r="E4" s="625"/>
-      <c r="F4" s="625"/>
-      <c r="G4" s="625"/>
-      <c r="H4" s="625"/>
-      <c r="I4" s="625"/>
-      <c r="L4" s="626"/>
+      <c r="A4" s="496"/>
+      <c r="B4" s="497"/>
+      <c r="C4" s="497"/>
+      <c r="D4" s="498"/>
+      <c r="E4" s="498"/>
+      <c r="F4" s="498"/>
+      <c r="G4" s="498"/>
+      <c r="H4" s="498"/>
+      <c r="I4" s="498"/>
+      <c r="L4" s="499"/>
       <c r="O4" s="475" t="s">
         <v>8</v>
       </c>
       <c r="P4" s="477"/>
     </row>
     <row r="5" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A5" s="627"/>
-      <c r="B5" s="628"/>
-      <c r="C5" s="628"/>
-      <c r="D5" s="628"/>
-      <c r="E5" s="628"/>
-      <c r="F5" s="628"/>
-      <c r="G5" s="628"/>
-      <c r="H5" s="628"/>
-      <c r="I5" s="628"/>
-      <c r="J5" s="628"/>
-      <c r="K5" s="628"/>
-      <c r="L5" s="629"/>
+      <c r="A5" s="500"/>
+      <c r="B5" s="501"/>
+      <c r="C5" s="501"/>
+      <c r="D5" s="501"/>
+      <c r="E5" s="501"/>
+      <c r="F5" s="501"/>
+      <c r="G5" s="501"/>
+      <c r="H5" s="501"/>
+      <c r="I5" s="501"/>
+      <c r="J5" s="501"/>
+      <c r="K5" s="501"/>
+      <c r="L5" s="502"/>
       <c r="O5" s="475" t="s">
         <v>11</v>
       </c>
       <c r="P5" s="477"/>
     </row>
     <row r="6" spans="1:16" ht="6.75" customHeight="1" thickTop="1">
-      <c r="A6" s="630"/>
-      <c r="B6" s="630"/>
-      <c r="C6" s="630"/>
-      <c r="D6" s="630"/>
-      <c r="E6" s="630"/>
-      <c r="F6" s="630"/>
-      <c r="G6" s="630"/>
-      <c r="H6" s="630"/>
-      <c r="I6" s="630"/>
-      <c r="J6" s="630"/>
-      <c r="K6" s="630"/>
-      <c r="L6" s="630"/>
+      <c r="A6" s="503"/>
+      <c r="B6" s="503"/>
+      <c r="C6" s="503"/>
+      <c r="D6" s="503"/>
+      <c r="E6" s="503"/>
+      <c r="F6" s="503"/>
+      <c r="G6" s="503"/>
+      <c r="H6" s="503"/>
+      <c r="I6" s="503"/>
+      <c r="J6" s="503"/>
+      <c r="K6" s="503"/>
+      <c r="L6" s="503"/>
       <c r="O6" s="478"/>
       <c r="P6" s="479"/>
     </row>
     <row r="7" spans="1:16" ht="15.9" customHeight="1">
-      <c r="A7" s="631" t="s">
+      <c r="A7" s="619" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="631"/>
-      <c r="C7" s="631"/>
-      <c r="D7" s="631"/>
-      <c r="E7" s="631"/>
-      <c r="F7" s="631"/>
-      <c r="G7" s="631"/>
-      <c r="H7" s="631"/>
-      <c r="I7" s="631"/>
-      <c r="J7" s="631"/>
-      <c r="K7" s="631"/>
-      <c r="L7" s="631"/>
+      <c r="B7" s="619"/>
+      <c r="C7" s="619"/>
+      <c r="D7" s="619"/>
+      <c r="E7" s="619"/>
+      <c r="F7" s="619"/>
+      <c r="G7" s="619"/>
+      <c r="H7" s="619"/>
+      <c r="I7" s="619"/>
+      <c r="J7" s="619"/>
+      <c r="K7" s="619"/>
+      <c r="L7" s="619"/>
       <c r="O7" s="475" t="s">
         <v>267</v>
       </c>
       <c r="P7" s="479"/>
     </row>
     <row r="8" spans="1:16" ht="15.9" customHeight="1">
-      <c r="A8" s="632" t="s">
+      <c r="A8" s="620" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="632"/>
-      <c r="C8" s="632"/>
-      <c r="D8" s="632"/>
-      <c r="E8" s="632"/>
-      <c r="F8" s="632"/>
-      <c r="G8" s="632"/>
-      <c r="H8" s="632"/>
-      <c r="I8" s="632"/>
-      <c r="J8" s="632"/>
-      <c r="K8" s="632"/>
-      <c r="L8" s="632"/>
+      <c r="B8" s="620"/>
+      <c r="C8" s="620"/>
+      <c r="D8" s="620"/>
+      <c r="E8" s="620"/>
+      <c r="F8" s="620"/>
+      <c r="G8" s="620"/>
+      <c r="H8" s="620"/>
+      <c r="I8" s="620"/>
+      <c r="J8" s="620"/>
+      <c r="K8" s="620"/>
+      <c r="L8" s="620"/>
       <c r="O8" s="475" t="s">
         <v>335</v>
       </c>
@@ -9454,18 +9519,18 @@
     <row r="10" spans="1:16" ht="15.9" customHeight="1">
       <c r="A10" s="490"/>
       <c r="B10" s="490"/>
-      <c r="D10" s="633" t="s">
+      <c r="D10" s="504" t="s">
         <v>290</v>
       </c>
-      <c r="E10" s="633" t="s">
+      <c r="E10" s="504" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="634"/>
-      <c r="G10" s="635" t="s">
+      <c r="F10" s="505"/>
+      <c r="G10" s="506" t="s">
         <v>291</v>
       </c>
-      <c r="H10" s="636"/>
-      <c r="I10" s="633" t="s">
+      <c r="H10" s="507"/>
+      <c r="I10" s="504" t="s">
         <v>292</v>
       </c>
       <c r="J10" s="490"/>
@@ -9478,12 +9543,12 @@
       <c r="A11" s="490"/>
       <c r="B11" s="490"/>
       <c r="C11" s="490"/>
-      <c r="D11" s="633"/>
-      <c r="E11" s="633"/>
-      <c r="F11" s="634"/>
-      <c r="G11" s="635"/>
-      <c r="H11" s="636"/>
-      <c r="I11" s="633"/>
+      <c r="D11" s="504"/>
+      <c r="E11" s="504"/>
+      <c r="F11" s="505"/>
+      <c r="G11" s="506"/>
+      <c r="H11" s="507"/>
+      <c r="I11" s="504"/>
       <c r="J11" s="490"/>
       <c r="K11" s="490"/>
       <c r="L11" s="490"/>
@@ -9507,18 +9572,18 @@
       <c r="P12" s="480"/>
     </row>
     <row r="13" spans="1:16" ht="7.5" customHeight="1">
-      <c r="A13" s="637"/>
-      <c r="B13" s="638"/>
-      <c r="C13" s="639"/>
-      <c r="D13" s="639"/>
-      <c r="E13" s="639"/>
-      <c r="F13" s="639"/>
-      <c r="G13" s="639"/>
-      <c r="H13" s="639"/>
-      <c r="I13" s="639"/>
-      <c r="J13" s="638"/>
-      <c r="K13" s="638"/>
-      <c r="L13" s="640"/>
+      <c r="A13" s="508"/>
+      <c r="B13" s="509"/>
+      <c r="C13" s="510"/>
+      <c r="D13" s="510"/>
+      <c r="E13" s="510"/>
+      <c r="F13" s="510"/>
+      <c r="G13" s="510"/>
+      <c r="H13" s="510"/>
+      <c r="I13" s="510"/>
+      <c r="J13" s="509"/>
+      <c r="K13" s="509"/>
+      <c r="L13" s="511"/>
       <c r="M13" s="87"/>
       <c r="O13" s="475" t="s">
         <v>27</v>
@@ -9526,39 +9591,39 @@
       <c r="P13" s="480"/>
     </row>
     <row r="14" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A14" s="641" t="s">
+      <c r="A14" s="621" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="642"/>
-      <c r="C14" s="642"/>
-      <c r="D14" s="642"/>
-      <c r="E14" s="642"/>
-      <c r="F14" s="642"/>
-      <c r="G14" s="642"/>
-      <c r="H14" s="642"/>
-      <c r="I14" s="642"/>
-      <c r="J14" s="642"/>
-      <c r="K14" s="642"/>
-      <c r="L14" s="643"/>
+      <c r="B14" s="622"/>
+      <c r="C14" s="622"/>
+      <c r="D14" s="622"/>
+      <c r="E14" s="622"/>
+      <c r="F14" s="622"/>
+      <c r="G14" s="622"/>
+      <c r="H14" s="622"/>
+      <c r="I14" s="622"/>
+      <c r="J14" s="622"/>
+      <c r="K14" s="622"/>
+      <c r="L14" s="623"/>
       <c r="M14" s="87"/>
       <c r="O14" s="478"/>
       <c r="P14" s="479"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="644" t="s">
+      <c r="A15" s="624" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="645"/>
-      <c r="C15" s="645"/>
-      <c r="D15" s="645"/>
-      <c r="E15" s="645"/>
-      <c r="F15" s="645"/>
-      <c r="G15" s="645"/>
-      <c r="H15" s="645"/>
-      <c r="I15" s="645"/>
-      <c r="J15" s="645"/>
-      <c r="K15" s="645"/>
-      <c r="L15" s="646"/>
+      <c r="B15" s="625"/>
+      <c r="C15" s="625"/>
+      <c r="D15" s="625"/>
+      <c r="E15" s="625"/>
+      <c r="F15" s="625"/>
+      <c r="G15" s="625"/>
+      <c r="H15" s="625"/>
+      <c r="I15" s="625"/>
+      <c r="J15" s="625"/>
+      <c r="K15" s="625"/>
+      <c r="L15" s="626"/>
       <c r="M15" s="87"/>
       <c r="O15" s="475" t="s">
         <v>104</v>
@@ -9566,18 +9631,18 @@
       <c r="P15" s="481"/>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1">
-      <c r="A16" s="647"/>
-      <c r="B16" s="648"/>
-      <c r="C16" s="649"/>
-      <c r="D16" s="649"/>
-      <c r="E16" s="649"/>
-      <c r="F16" s="649"/>
-      <c r="G16" s="649"/>
-      <c r="H16" s="649"/>
-      <c r="I16" s="649"/>
-      <c r="J16" s="648"/>
-      <c r="K16" s="648"/>
-      <c r="L16" s="650"/>
+      <c r="A16" s="512"/>
+      <c r="B16" s="513"/>
+      <c r="C16" s="514"/>
+      <c r="D16" s="514"/>
+      <c r="E16" s="514"/>
+      <c r="F16" s="514"/>
+      <c r="G16" s="514"/>
+      <c r="H16" s="514"/>
+      <c r="I16" s="514"/>
+      <c r="J16" s="513"/>
+      <c r="K16" s="513"/>
+      <c r="L16" s="515"/>
       <c r="M16" s="87"/>
       <c r="O16" s="475" t="s">
         <v>25</v>
@@ -9585,107 +9650,107 @@
       <c r="P16" s="481"/>
     </row>
     <row r="17" spans="1:19" ht="15.9" customHeight="1">
-      <c r="A17" s="536" t="s">
+      <c r="A17" s="617" t="s">
         <v>293</v>
       </c>
-      <c r="B17" s="537"/>
-      <c r="C17" s="537"/>
-      <c r="D17" s="537"/>
-      <c r="E17" s="537"/>
-      <c r="F17" s="537"/>
-      <c r="G17" s="537"/>
-      <c r="H17" s="537"/>
-      <c r="I17" s="537"/>
+      <c r="B17" s="618"/>
+      <c r="C17" s="618"/>
+      <c r="D17" s="618"/>
+      <c r="E17" s="618"/>
+      <c r="F17" s="618"/>
+      <c r="G17" s="618"/>
+      <c r="H17" s="618"/>
+      <c r="I17" s="618"/>
       <c r="J17" s="456"/>
       <c r="K17" s="456"/>
-      <c r="L17" s="651"/>
+      <c r="L17" s="516"/>
       <c r="O17" s="475" t="s">
         <v>29</v>
       </c>
       <c r="P17" s="482"/>
     </row>
     <row r="18" spans="1:19" ht="18" customHeight="1">
-      <c r="A18" s="652" t="s">
+      <c r="A18" s="517" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="653"/>
-      <c r="C18" s="653"/>
-      <c r="D18" s="653"/>
-      <c r="E18" s="653"/>
-      <c r="F18" s="653"/>
-      <c r="G18" s="653"/>
-      <c r="H18" s="653"/>
-      <c r="I18" s="653"/>
-      <c r="J18" s="654"/>
+      <c r="B18" s="518"/>
+      <c r="C18" s="518"/>
+      <c r="D18" s="518"/>
+      <c r="E18" s="518"/>
+      <c r="F18" s="518"/>
+      <c r="G18" s="518"/>
+      <c r="H18" s="518"/>
+      <c r="I18" s="518"/>
+      <c r="J18" s="519"/>
       <c r="K18" s="456"/>
-      <c r="L18" s="651"/>
+      <c r="L18" s="516"/>
     </row>
     <row r="19" spans="1:19" ht="18" customHeight="1">
-      <c r="A19" s="652" t="s">
+      <c r="A19" s="517" t="s">
         <v>294</v>
       </c>
-      <c r="B19" s="653"/>
-      <c r="C19" s="653"/>
-      <c r="D19" s="653"/>
-      <c r="E19" s="653"/>
-      <c r="F19" s="653"/>
-      <c r="G19" s="653"/>
-      <c r="H19" s="653"/>
-      <c r="I19" s="653"/>
-      <c r="J19" s="654"/>
+      <c r="B19" s="518"/>
+      <c r="C19" s="518"/>
+      <c r="D19" s="518"/>
+      <c r="E19" s="518"/>
+      <c r="F19" s="518"/>
+      <c r="G19" s="518"/>
+      <c r="H19" s="518"/>
+      <c r="I19" s="518"/>
+      <c r="J19" s="519"/>
       <c r="K19" s="456"/>
-      <c r="L19" s="651"/>
+      <c r="L19" s="516"/>
     </row>
     <row r="20" spans="1:19" ht="18" customHeight="1">
-      <c r="A20" s="652" t="s">
+      <c r="A20" s="517" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="653"/>
-      <c r="C20" s="653"/>
-      <c r="D20" s="653"/>
-      <c r="E20" s="653"/>
-      <c r="F20" s="653"/>
-      <c r="G20" s="653"/>
-      <c r="H20" s="653"/>
-      <c r="I20" s="653"/>
-      <c r="J20" s="654"/>
+      <c r="B20" s="518"/>
+      <c r="C20" s="518"/>
+      <c r="D20" s="518"/>
+      <c r="E20" s="518"/>
+      <c r="F20" s="518"/>
+      <c r="G20" s="518"/>
+      <c r="H20" s="518"/>
+      <c r="I20" s="518"/>
+      <c r="J20" s="519"/>
       <c r="K20" s="456"/>
-      <c r="L20" s="651"/>
+      <c r="L20" s="516"/>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1">
-      <c r="A21" s="652" t="s">
+      <c r="A21" s="517" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="653"/>
-      <c r="C21" s="653"/>
-      <c r="D21" s="653"/>
-      <c r="E21" s="653"/>
-      <c r="F21" s="653"/>
-      <c r="G21" s="653"/>
-      <c r="H21" s="653"/>
-      <c r="I21" s="653"/>
-      <c r="J21" s="654"/>
+      <c r="B21" s="518"/>
+      <c r="C21" s="518"/>
+      <c r="D21" s="518"/>
+      <c r="E21" s="518"/>
+      <c r="F21" s="518"/>
+      <c r="G21" s="518"/>
+      <c r="H21" s="518"/>
+      <c r="I21" s="518"/>
+      <c r="J21" s="519"/>
       <c r="K21" s="456"/>
-      <c r="L21" s="651"/>
+      <c r="L21" s="516"/>
     </row>
     <row r="22" spans="1:19" ht="18" customHeight="1">
-      <c r="A22" s="655" t="s">
+      <c r="A22" s="520" t="s">
         <v>332</v>
       </c>
-      <c r="B22" s="653"/>
-      <c r="C22" s="653"/>
-      <c r="D22" s="653"/>
-      <c r="E22" s="653"/>
-      <c r="F22" s="653"/>
-      <c r="G22" s="653"/>
-      <c r="H22" s="653"/>
-      <c r="I22" s="653"/>
+      <c r="B22" s="518"/>
+      <c r="C22" s="518"/>
+      <c r="D22" s="518"/>
+      <c r="E22" s="518"/>
+      <c r="F22" s="518"/>
+      <c r="G22" s="518"/>
+      <c r="H22" s="518"/>
+      <c r="I22" s="518"/>
       <c r="J22" s="456"/>
       <c r="K22" s="456"/>
-      <c r="L22" s="651"/>
+      <c r="L22" s="516"/>
     </row>
     <row r="23" spans="1:19" ht="14.4" customHeight="1">
-      <c r="A23" s="656"/>
+      <c r="A23" s="521"/>
       <c r="B23" s="457"/>
       <c r="C23" s="457"/>
       <c r="D23" s="457"/>
@@ -9696,15 +9761,15 @@
       <c r="I23" s="457"/>
       <c r="J23" s="456"/>
       <c r="K23" s="456"/>
-      <c r="L23" s="651"/>
+      <c r="L23" s="516"/>
     </row>
     <row r="24" spans="1:19" ht="15.9" customHeight="1">
-      <c r="A24" s="536" t="s">
+      <c r="A24" s="617" t="s">
         <v>295</v>
       </c>
-      <c r="B24" s="537"/>
-      <c r="C24" s="537"/>
-      <c r="D24" s="537"/>
+      <c r="B24" s="618"/>
+      <c r="C24" s="618"/>
+      <c r="D24" s="618"/>
       <c r="E24" s="457"/>
       <c r="F24" s="457"/>
       <c r="G24" s="457"/>
@@ -9712,654 +9777,654 @@
       <c r="I24" s="457"/>
       <c r="J24" s="456"/>
       <c r="K24" s="456"/>
-      <c r="L24" s="651"/>
+      <c r="L24" s="516"/>
     </row>
     <row r="25" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A25" s="538" t="s">
+      <c r="A25" s="627" t="s">
         <v>296</v>
       </c>
-      <c r="B25" s="538"/>
-      <c r="C25" s="538"/>
-      <c r="D25" s="538"/>
-      <c r="E25" s="539"/>
-      <c r="F25" s="539"/>
+      <c r="B25" s="627"/>
+      <c r="C25" s="627"/>
+      <c r="D25" s="627"/>
+      <c r="E25" s="628"/>
+      <c r="F25" s="628"/>
       <c r="G25" s="458"/>
-      <c r="H25" s="540" t="s">
+      <c r="H25" s="629" t="s">
         <v>325</v>
       </c>
-      <c r="I25" s="541"/>
-      <c r="J25" s="542"/>
-      <c r="K25" s="657"/>
-      <c r="L25" s="651"/>
+      <c r="I25" s="630"/>
+      <c r="J25" s="631"/>
+      <c r="K25" s="522"/>
+      <c r="L25" s="516"/>
     </row>
     <row r="26" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A26" s="538" t="s">
+      <c r="A26" s="627" t="s">
         <v>297</v>
       </c>
-      <c r="B26" s="538"/>
-      <c r="C26" s="538"/>
-      <c r="D26" s="538"/>
-      <c r="E26" s="539"/>
-      <c r="F26" s="539"/>
+      <c r="B26" s="627"/>
+      <c r="C26" s="627"/>
+      <c r="D26" s="627"/>
+      <c r="E26" s="628"/>
+      <c r="F26" s="628"/>
       <c r="G26" s="458"/>
-      <c r="H26" s="543" t="s">
+      <c r="H26" s="632" t="s">
         <v>326</v>
       </c>
-      <c r="I26" s="543"/>
+      <c r="I26" s="632"/>
       <c r="J26" s="459"/>
-      <c r="K26" s="658"/>
-      <c r="L26" s="651"/>
+      <c r="K26" s="523"/>
+      <c r="L26" s="516"/>
     </row>
     <row r="27" spans="1:19" ht="22.2" customHeight="1">
-      <c r="A27" s="538" t="s">
+      <c r="A27" s="627" t="s">
         <v>298</v>
       </c>
-      <c r="B27" s="538"/>
-      <c r="C27" s="538"/>
-      <c r="D27" s="538"/>
-      <c r="E27" s="539"/>
-      <c r="F27" s="539"/>
+      <c r="B27" s="627"/>
+      <c r="C27" s="627"/>
+      <c r="D27" s="627"/>
+      <c r="E27" s="628"/>
+      <c r="F27" s="628"/>
       <c r="G27" s="458"/>
       <c r="H27" s="471"/>
       <c r="I27" s="472"/>
       <c r="J27" s="473"/>
       <c r="K27" s="473"/>
-      <c r="L27" s="651"/>
+      <c r="L27" s="516"/>
       <c r="M27" s="87"/>
     </row>
     <row r="28" spans="1:19" ht="22.2" customHeight="1">
-      <c r="A28" s="538" t="s">
+      <c r="A28" s="627" t="s">
         <v>327</v>
       </c>
-      <c r="B28" s="538"/>
-      <c r="C28" s="538"/>
-      <c r="D28" s="538"/>
-      <c r="E28" s="539"/>
-      <c r="F28" s="539"/>
-      <c r="L28" s="659"/>
+      <c r="B28" s="627"/>
+      <c r="C28" s="627"/>
+      <c r="D28" s="627"/>
+      <c r="E28" s="628"/>
+      <c r="F28" s="628"/>
+      <c r="L28" s="524"/>
       <c r="M28" s="87"/>
     </row>
     <row r="29" spans="1:19" ht="22.2" customHeight="1">
-      <c r="A29" s="660"/>
-      <c r="B29" s="661"/>
-      <c r="C29" s="661"/>
-      <c r="D29" s="661"/>
-      <c r="E29" s="661"/>
-      <c r="F29" s="661"/>
-      <c r="G29" s="662"/>
-      <c r="H29" s="662"/>
-      <c r="I29" s="662"/>
-      <c r="J29" s="663"/>
-      <c r="K29" s="663"/>
-      <c r="L29" s="664"/>
+      <c r="A29" s="525"/>
+      <c r="B29" s="526"/>
+      <c r="C29" s="526"/>
+      <c r="D29" s="526"/>
+      <c r="E29" s="526"/>
+      <c r="F29" s="526"/>
+      <c r="G29" s="527"/>
+      <c r="H29" s="527"/>
+      <c r="I29" s="527"/>
+      <c r="J29" s="528"/>
+      <c r="K29" s="528"/>
+      <c r="L29" s="529"/>
       <c r="M29" s="87"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A30" s="665"/>
-      <c r="B30" s="666" t="s">
+      <c r="A30" s="530"/>
+      <c r="B30" s="636" t="s">
         <v>300</v>
       </c>
-      <c r="C30" s="666"/>
-      <c r="D30" s="666"/>
-      <c r="E30" s="666"/>
-      <c r="F30" s="666"/>
-      <c r="G30" s="666"/>
-      <c r="H30" s="667" t="s">
+      <c r="C30" s="636"/>
+      <c r="D30" s="636"/>
+      <c r="E30" s="636"/>
+      <c r="F30" s="636"/>
+      <c r="G30" s="636"/>
+      <c r="H30" s="531" t="s">
         <v>301</v>
       </c>
-      <c r="I30" s="667" t="s">
+      <c r="I30" s="531" t="s">
         <v>302</v>
       </c>
-      <c r="J30" s="668"/>
-      <c r="K30" s="668"/>
-      <c r="L30" s="669"/>
+      <c r="J30" s="637"/>
+      <c r="K30" s="637"/>
+      <c r="L30" s="532"/>
       <c r="M30" s="87"/>
     </row>
     <row r="31" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A31" s="670"/>
-      <c r="B31" s="671">
+      <c r="A31" s="533"/>
+      <c r="B31" s="534">
         <v>1</v>
       </c>
-      <c r="C31" s="672" t="s">
+      <c r="C31" s="633" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="673"/>
-      <c r="E31" s="673"/>
-      <c r="F31" s="673"/>
-      <c r="G31" s="674"/>
-      <c r="H31" s="675" t="s">
+      <c r="D31" s="634"/>
+      <c r="E31" s="634"/>
+      <c r="F31" s="634"/>
+      <c r="G31" s="635"/>
+      <c r="H31" s="535" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="676"/>
-      <c r="J31" s="677"/>
-      <c r="K31" s="677"/>
-      <c r="L31" s="678"/>
+      <c r="I31" s="536"/>
+      <c r="J31" s="537"/>
+      <c r="K31" s="537"/>
+      <c r="L31" s="538"/>
       <c r="M31" s="87"/>
     </row>
     <row r="32" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A32" s="670"/>
-      <c r="B32" s="679">
+      <c r="A32" s="533"/>
+      <c r="B32" s="539">
         <v>2</v>
       </c>
-      <c r="C32" s="672" t="s">
+      <c r="C32" s="633" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="673"/>
-      <c r="E32" s="673"/>
-      <c r="F32" s="673"/>
-      <c r="G32" s="674"/>
-      <c r="H32" s="675" t="s">
+      <c r="D32" s="634"/>
+      <c r="E32" s="634"/>
+      <c r="F32" s="634"/>
+      <c r="G32" s="635"/>
+      <c r="H32" s="535" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="676"/>
-      <c r="J32" s="677"/>
-      <c r="K32" s="677"/>
-      <c r="L32" s="678"/>
+      <c r="I32" s="536"/>
+      <c r="J32" s="537"/>
+      <c r="K32" s="537"/>
+      <c r="L32" s="538"/>
       <c r="M32" s="87"/>
       <c r="S32" s="460"/>
     </row>
     <row r="33" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A33" s="670"/>
-      <c r="B33" s="679">
+      <c r="A33" s="533"/>
+      <c r="B33" s="539">
         <v>3</v>
       </c>
-      <c r="C33" s="672" t="s">
+      <c r="C33" s="633" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="673"/>
-      <c r="E33" s="673"/>
-      <c r="F33" s="673"/>
-      <c r="G33" s="674"/>
-      <c r="H33" s="675" t="s">
+      <c r="D33" s="634"/>
+      <c r="E33" s="634"/>
+      <c r="F33" s="634"/>
+      <c r="G33" s="635"/>
+      <c r="H33" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I33" s="676"/>
-      <c r="J33" s="677"/>
-      <c r="K33" s="677"/>
-      <c r="L33" s="680"/>
+      <c r="I33" s="536"/>
+      <c r="J33" s="537"/>
+      <c r="K33" s="537"/>
+      <c r="L33" s="540"/>
       <c r="M33" s="461"/>
       <c r="W33" s="460"/>
     </row>
     <row r="34" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A34" s="670"/>
-      <c r="B34" s="671">
+      <c r="A34" s="533"/>
+      <c r="B34" s="534">
         <v>4</v>
       </c>
-      <c r="C34" s="672" t="s">
+      <c r="C34" s="633" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="673"/>
-      <c r="E34" s="673"/>
-      <c r="F34" s="673"/>
-      <c r="G34" s="674"/>
-      <c r="H34" s="675" t="s">
+      <c r="D34" s="634"/>
+      <c r="E34" s="634"/>
+      <c r="F34" s="634"/>
+      <c r="G34" s="635"/>
+      <c r="H34" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I34" s="676"/>
-      <c r="J34" s="677"/>
-      <c r="K34" s="677"/>
-      <c r="L34" s="680"/>
+      <c r="I34" s="536"/>
+      <c r="J34" s="537"/>
+      <c r="K34" s="537"/>
+      <c r="L34" s="540"/>
       <c r="M34" s="461"/>
       <c r="O34" s="462"/>
       <c r="P34" s="462"/>
       <c r="W34" s="460"/>
     </row>
     <row r="35" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A35" s="670"/>
-      <c r="B35" s="679">
+      <c r="A35" s="533"/>
+      <c r="B35" s="539">
         <v>5</v>
       </c>
-      <c r="C35" s="672" t="s">
+      <c r="C35" s="633" t="s">
         <v>304</v>
       </c>
-      <c r="D35" s="673"/>
-      <c r="E35" s="673"/>
-      <c r="F35" s="673"/>
-      <c r="G35" s="674"/>
-      <c r="H35" s="675" t="s">
+      <c r="D35" s="634"/>
+      <c r="E35" s="634"/>
+      <c r="F35" s="634"/>
+      <c r="G35" s="635"/>
+      <c r="H35" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I35" s="676"/>
-      <c r="J35" s="677"/>
-      <c r="K35" s="677"/>
-      <c r="L35" s="681"/>
+      <c r="I35" s="536"/>
+      <c r="J35" s="537"/>
+      <c r="K35" s="537"/>
+      <c r="L35" s="541"/>
       <c r="M35" s="461"/>
       <c r="O35" s="462"/>
       <c r="P35" s="462"/>
       <c r="W35" s="460"/>
     </row>
     <row r="36" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A36" s="670"/>
-      <c r="B36" s="671">
+      <c r="A36" s="533"/>
+      <c r="B36" s="534">
         <v>6</v>
       </c>
-      <c r="C36" s="672" t="s">
+      <c r="C36" s="633" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="673"/>
-      <c r="E36" s="673"/>
-      <c r="F36" s="673"/>
-      <c r="G36" s="674"/>
-      <c r="H36" s="675" t="s">
+      <c r="D36" s="634"/>
+      <c r="E36" s="634"/>
+      <c r="F36" s="634"/>
+      <c r="G36" s="635"/>
+      <c r="H36" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I36" s="676"/>
-      <c r="J36" s="677"/>
-      <c r="K36" s="677"/>
-      <c r="L36" s="681"/>
+      <c r="I36" s="536"/>
+      <c r="J36" s="537"/>
+      <c r="K36" s="537"/>
+      <c r="L36" s="541"/>
       <c r="M36" s="461"/>
       <c r="O36" s="462"/>
       <c r="P36" s="462"/>
       <c r="W36" s="460"/>
     </row>
     <row r="37" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A37" s="670"/>
-      <c r="B37" s="679">
+      <c r="A37" s="533"/>
+      <c r="B37" s="539">
         <v>7</v>
       </c>
-      <c r="C37" s="672" t="s">
+      <c r="C37" s="633" t="s">
         <v>333</v>
       </c>
-      <c r="D37" s="673"/>
-      <c r="E37" s="673"/>
-      <c r="F37" s="673"/>
-      <c r="G37" s="674"/>
-      <c r="H37" s="675" t="s">
+      <c r="D37" s="634"/>
+      <c r="E37" s="634"/>
+      <c r="F37" s="634"/>
+      <c r="G37" s="635"/>
+      <c r="H37" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I37" s="676"/>
-      <c r="J37" s="677"/>
-      <c r="K37" s="677"/>
-      <c r="L37" s="681"/>
+      <c r="I37" s="536"/>
+      <c r="J37" s="537"/>
+      <c r="K37" s="537"/>
+      <c r="L37" s="541"/>
       <c r="M37" s="461"/>
       <c r="N37" s="463"/>
       <c r="O37" s="462"/>
       <c r="P37" s="462"/>
     </row>
     <row r="38" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A38" s="670"/>
-      <c r="B38" s="679">
+      <c r="A38" s="533"/>
+      <c r="B38" s="539">
         <v>8</v>
       </c>
-      <c r="C38" s="672" t="s">
+      <c r="C38" s="633" t="s">
         <v>305</v>
       </c>
-      <c r="D38" s="673"/>
-      <c r="E38" s="673"/>
-      <c r="F38" s="673"/>
-      <c r="G38" s="674"/>
-      <c r="H38" s="675" t="s">
+      <c r="D38" s="634"/>
+      <c r="E38" s="634"/>
+      <c r="F38" s="634"/>
+      <c r="G38" s="635"/>
+      <c r="H38" s="535" t="s">
         <v>193</v>
       </c>
-      <c r="I38" s="676"/>
-      <c r="J38" s="677"/>
-      <c r="K38" s="677"/>
-      <c r="L38" s="681"/>
+      <c r="I38" s="536"/>
+      <c r="J38" s="537"/>
+      <c r="K38" s="537"/>
+      <c r="L38" s="541"/>
       <c r="M38" s="461"/>
       <c r="N38" s="464"/>
       <c r="O38" s="465"/>
       <c r="P38" s="465"/>
     </row>
     <row r="39" spans="1:23" ht="21.75" customHeight="1">
-      <c r="A39" s="670"/>
-      <c r="B39" s="671">
+      <c r="A39" s="533"/>
+      <c r="B39" s="534">
         <v>9</v>
       </c>
-      <c r="C39" s="672" t="s">
+      <c r="C39" s="633" t="s">
         <v>306</v>
       </c>
-      <c r="D39" s="673"/>
-      <c r="E39" s="673"/>
-      <c r="F39" s="673"/>
-      <c r="G39" s="674"/>
-      <c r="H39" s="675" t="s">
+      <c r="D39" s="634"/>
+      <c r="E39" s="634"/>
+      <c r="F39" s="634"/>
+      <c r="G39" s="635"/>
+      <c r="H39" s="535" t="s">
         <v>56</v>
       </c>
-      <c r="I39" s="676"/>
-      <c r="J39" s="677"/>
-      <c r="K39" s="677"/>
-      <c r="L39" s="681"/>
+      <c r="I39" s="536"/>
+      <c r="J39" s="537"/>
+      <c r="K39" s="537"/>
+      <c r="L39" s="541"/>
       <c r="M39" s="461"/>
       <c r="N39" s="466"/>
       <c r="O39" s="204"/>
     </row>
     <row r="40" spans="1:23" ht="6.75" customHeight="1">
-      <c r="A40" s="670"/>
-      <c r="B40" s="662"/>
-      <c r="C40" s="662"/>
-      <c r="D40" s="662"/>
-      <c r="E40" s="662"/>
-      <c r="F40" s="662"/>
-      <c r="I40" s="682"/>
-      <c r="J40" s="683"/>
-      <c r="K40" s="683"/>
-      <c r="L40" s="681"/>
+      <c r="A40" s="533"/>
+      <c r="B40" s="527"/>
+      <c r="C40" s="527"/>
+      <c r="D40" s="527"/>
+      <c r="E40" s="527"/>
+      <c r="F40" s="527"/>
+      <c r="I40" s="542"/>
+      <c r="J40" s="543"/>
+      <c r="K40" s="543"/>
+      <c r="L40" s="541"/>
       <c r="M40" s="87"/>
       <c r="N40" s="466"/>
       <c r="O40" s="204"/>
       <c r="W40" s="460"/>
     </row>
     <row r="41" spans="1:23" ht="17.25" customHeight="1">
-      <c r="A41" s="670"/>
-      <c r="B41" s="684" t="s">
+      <c r="A41" s="533"/>
+      <c r="B41" s="642" t="s">
         <v>307</v>
       </c>
-      <c r="C41" s="684"/>
-      <c r="D41" s="684"/>
-      <c r="E41" s="684"/>
-      <c r="F41" s="684"/>
-      <c r="G41" s="685"/>
-      <c r="H41" s="686" t="s">
+      <c r="C41" s="642"/>
+      <c r="D41" s="642"/>
+      <c r="E41" s="642"/>
+      <c r="F41" s="642"/>
+      <c r="G41" s="544"/>
+      <c r="H41" s="643" t="s">
         <v>308</v>
       </c>
-      <c r="I41" s="687"/>
-      <c r="J41" s="688"/>
-      <c r="K41" s="688"/>
-      <c r="L41" s="687"/>
+      <c r="I41" s="644"/>
+      <c r="J41" s="645"/>
+      <c r="K41" s="645"/>
+      <c r="L41" s="644"/>
       <c r="M41" s="87"/>
       <c r="W41" s="460"/>
     </row>
     <row r="42" spans="1:23" ht="26.25" customHeight="1">
-      <c r="A42" s="670"/>
-      <c r="B42" s="689" t="s">
+      <c r="A42" s="533"/>
+      <c r="B42" s="646" t="s">
         <v>309</v>
       </c>
-      <c r="C42" s="689"/>
-      <c r="D42" s="689"/>
-      <c r="E42" s="690" t="s">
+      <c r="C42" s="646"/>
+      <c r="D42" s="646"/>
+      <c r="E42" s="545" t="s">
         <v>310</v>
       </c>
-      <c r="F42" s="690" t="s">
+      <c r="F42" s="545" t="s">
         <v>311</v>
       </c>
-      <c r="G42" s="685"/>
-      <c r="H42" s="691" t="s">
+      <c r="G42" s="544"/>
+      <c r="H42" s="647" t="s">
         <v>312</v>
       </c>
-      <c r="I42" s="691"/>
-      <c r="J42" s="692"/>
-      <c r="K42" s="692"/>
-      <c r="L42" s="692"/>
+      <c r="I42" s="647"/>
+      <c r="J42" s="648"/>
+      <c r="K42" s="648"/>
+      <c r="L42" s="648"/>
       <c r="M42" s="87"/>
       <c r="W42" s="460"/>
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1">
-      <c r="A43" s="670"/>
-      <c r="B43" s="693" t="s">
+      <c r="A43" s="533"/>
+      <c r="B43" s="663" t="s">
         <v>313</v>
       </c>
-      <c r="C43" s="693"/>
-      <c r="D43" s="693"/>
-      <c r="E43" s="694" t="s">
+      <c r="C43" s="663"/>
+      <c r="D43" s="663"/>
+      <c r="E43" s="546" t="s">
         <v>146</v>
       </c>
-      <c r="F43" s="694" t="s">
+      <c r="F43" s="546" t="s">
         <v>314</v>
       </c>
-      <c r="G43" s="685"/>
-      <c r="H43" s="691" t="s">
+      <c r="G43" s="544"/>
+      <c r="H43" s="647" t="s">
         <v>315</v>
       </c>
-      <c r="I43" s="691"/>
-      <c r="J43" s="695"/>
-      <c r="K43" s="695"/>
-      <c r="L43" s="696"/>
+      <c r="I43" s="647"/>
+      <c r="J43" s="638"/>
+      <c r="K43" s="638"/>
+      <c r="L43" s="639"/>
       <c r="M43" s="87"/>
       <c r="W43" s="460"/>
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1">
-      <c r="A44" s="670"/>
-      <c r="B44" s="693" t="s">
+      <c r="A44" s="533"/>
+      <c r="B44" s="663" t="s">
         <v>316</v>
       </c>
-      <c r="C44" s="693"/>
-      <c r="D44" s="693"/>
-      <c r="E44" s="694" t="s">
+      <c r="C44" s="663"/>
+      <c r="D44" s="663"/>
+      <c r="E44" s="546" t="s">
         <v>148</v>
       </c>
-      <c r="F44" s="694" t="s">
+      <c r="F44" s="546" t="s">
         <v>314</v>
       </c>
-      <c r="G44" s="685"/>
-      <c r="H44" s="691"/>
-      <c r="I44" s="691"/>
-      <c r="J44" s="697"/>
-      <c r="K44" s="697"/>
-      <c r="L44" s="698"/>
+      <c r="G44" s="544"/>
+      <c r="H44" s="647"/>
+      <c r="I44" s="647"/>
+      <c r="J44" s="640"/>
+      <c r="K44" s="640"/>
+      <c r="L44" s="641"/>
       <c r="M44" s="87"/>
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1">
-      <c r="A45" s="670"/>
-      <c r="B45" s="699" t="s">
+      <c r="A45" s="533"/>
+      <c r="B45" s="659" t="s">
         <v>317</v>
       </c>
-      <c r="C45" s="699"/>
-      <c r="D45" s="699"/>
-      <c r="E45" s="694" t="s">
+      <c r="C45" s="659"/>
+      <c r="D45" s="659"/>
+      <c r="E45" s="546" t="s">
         <v>150</v>
       </c>
-      <c r="F45" s="694" t="s">
+      <c r="F45" s="546" t="s">
         <v>314</v>
       </c>
-      <c r="G45" s="685"/>
-      <c r="H45" s="691" t="s">
+      <c r="G45" s="544"/>
+      <c r="H45" s="647" t="s">
         <v>318</v>
       </c>
-      <c r="I45" s="691"/>
-      <c r="J45" s="695"/>
-      <c r="K45" s="695"/>
-      <c r="L45" s="696"/>
+      <c r="I45" s="647"/>
+      <c r="J45" s="638"/>
+      <c r="K45" s="638"/>
+      <c r="L45" s="639"/>
       <c r="M45" s="87"/>
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1">
-      <c r="A46" s="670"/>
-      <c r="B46" s="684" t="s">
+      <c r="A46" s="533"/>
+      <c r="B46" s="642" t="s">
         <v>319</v>
       </c>
-      <c r="C46" s="684"/>
-      <c r="D46" s="684"/>
-      <c r="E46" s="684"/>
-      <c r="F46" s="684"/>
-      <c r="G46" s="685"/>
-      <c r="H46" s="691"/>
-      <c r="I46" s="691"/>
-      <c r="J46" s="697"/>
-      <c r="K46" s="697"/>
-      <c r="L46" s="698"/>
+      <c r="C46" s="642"/>
+      <c r="D46" s="642"/>
+      <c r="E46" s="642"/>
+      <c r="F46" s="642"/>
+      <c r="G46" s="544"/>
+      <c r="H46" s="647"/>
+      <c r="I46" s="647"/>
+      <c r="J46" s="640"/>
+      <c r="K46" s="640"/>
+      <c r="L46" s="641"/>
       <c r="M46" s="87"/>
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1">
-      <c r="A47" s="670"/>
-      <c r="B47" s="699" t="s">
+      <c r="A47" s="533"/>
+      <c r="B47" s="659" t="s">
         <v>320</v>
       </c>
-      <c r="C47" s="699"/>
-      <c r="D47" s="699"/>
-      <c r="E47" s="694" t="s">
+      <c r="C47" s="659"/>
+      <c r="D47" s="659"/>
+      <c r="E47" s="546" t="s">
         <v>152</v>
       </c>
-      <c r="F47" s="694" t="s">
+      <c r="F47" s="546" t="s">
         <v>321</v>
       </c>
-      <c r="G47" s="685"/>
-      <c r="H47" s="700"/>
-      <c r="I47" s="700"/>
-      <c r="J47" s="701"/>
-      <c r="K47" s="701"/>
-      <c r="L47" s="702"/>
+      <c r="G47" s="544"/>
+      <c r="H47" s="660"/>
+      <c r="I47" s="660"/>
+      <c r="J47" s="661"/>
+      <c r="K47" s="661"/>
+      <c r="L47" s="662"/>
       <c r="M47" s="87"/>
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1">
-      <c r="A48" s="670"/>
-      <c r="B48" s="693" t="s">
+      <c r="A48" s="533"/>
+      <c r="B48" s="663" t="s">
         <v>153</v>
       </c>
-      <c r="C48" s="693"/>
-      <c r="D48" s="693"/>
-      <c r="E48" s="694" t="s">
+      <c r="C48" s="663"/>
+      <c r="D48" s="663"/>
+      <c r="E48" s="546" t="s">
         <v>150</v>
       </c>
-      <c r="F48" s="694" t="s">
+      <c r="F48" s="546" t="s">
         <v>321</v>
       </c>
-      <c r="G48" s="685"/>
-      <c r="H48" s="700"/>
-      <c r="I48" s="700"/>
-      <c r="J48" s="701"/>
-      <c r="K48" s="701"/>
-      <c r="L48" s="702"/>
+      <c r="G48" s="544"/>
+      <c r="H48" s="660"/>
+      <c r="I48" s="660"/>
+      <c r="J48" s="661"/>
+      <c r="K48" s="661"/>
+      <c r="L48" s="662"/>
       <c r="M48" s="87"/>
     </row>
     <row r="49" spans="1:13" ht="15" customHeight="1">
-      <c r="A49" s="670"/>
-      <c r="B49" s="693" t="s">
+      <c r="A49" s="533"/>
+      <c r="B49" s="663" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="693"/>
-      <c r="D49" s="693"/>
-      <c r="E49" s="694" t="s">
+      <c r="C49" s="663"/>
+      <c r="D49" s="663"/>
+      <c r="E49" s="546" t="s">
         <v>150</v>
       </c>
-      <c r="F49" s="694" t="s">
+      <c r="F49" s="546" t="s">
         <v>321</v>
       </c>
-      <c r="G49" s="685"/>
-      <c r="H49" s="703"/>
-      <c r="I49" s="703"/>
-      <c r="J49" s="704"/>
-      <c r="K49" s="704"/>
-      <c r="L49" s="705"/>
+      <c r="G49" s="544"/>
+      <c r="H49" s="547"/>
+      <c r="I49" s="547"/>
+      <c r="J49" s="548"/>
+      <c r="K49" s="548"/>
+      <c r="L49" s="549"/>
       <c r="M49" s="87"/>
     </row>
     <row r="50" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A50" s="706"/>
-      <c r="B50" s="707" t="s">
+      <c r="A50" s="550"/>
+      <c r="B50" s="551" t="s">
         <v>322</v>
       </c>
-      <c r="C50" s="708"/>
-      <c r="D50" s="708"/>
-      <c r="E50" s="709"/>
-      <c r="F50" s="709"/>
-      <c r="G50" s="710"/>
-      <c r="H50" s="711"/>
-      <c r="I50" s="711"/>
-      <c r="J50" s="712"/>
-      <c r="K50" s="712"/>
-      <c r="L50" s="713"/>
+      <c r="C50" s="552"/>
+      <c r="D50" s="552"/>
+      <c r="E50" s="553"/>
+      <c r="F50" s="553"/>
+      <c r="G50" s="554"/>
+      <c r="H50" s="555"/>
+      <c r="I50" s="555"/>
+      <c r="J50" s="556"/>
+      <c r="K50" s="556"/>
+      <c r="L50" s="557"/>
       <c r="M50" s="87"/>
     </row>
     <row r="51" spans="1:13" ht="7.5" customHeight="1">
-      <c r="A51" s="714"/>
+      <c r="A51" s="558"/>
       <c r="B51" s="460"/>
       <c r="C51" s="460"/>
       <c r="D51" s="460"/>
       <c r="E51" s="460"/>
       <c r="F51" s="460"/>
       <c r="G51" s="460"/>
-      <c r="H51" s="715"/>
-      <c r="I51" s="716"/>
+      <c r="H51" s="559"/>
+      <c r="I51" s="560"/>
       <c r="J51" s="460"/>
       <c r="K51" s="460"/>
       <c r="L51" s="460"/>
       <c r="M51" s="87"/>
     </row>
     <row r="52" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A52" s="717" t="s">
+      <c r="A52" s="561" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="712"/>
-      <c r="C52" s="712"/>
-      <c r="D52" s="712"/>
-      <c r="E52" s="712"/>
-      <c r="F52" s="712"/>
-      <c r="G52" s="712"/>
-      <c r="H52" s="711"/>
-      <c r="I52" s="711"/>
-      <c r="J52" s="711"/>
-      <c r="K52" s="711"/>
-      <c r="L52" s="711"/>
+      <c r="B52" s="556"/>
+      <c r="C52" s="556"/>
+      <c r="D52" s="556"/>
+      <c r="E52" s="556"/>
+      <c r="F52" s="556"/>
+      <c r="G52" s="556"/>
+      <c r="H52" s="555"/>
+      <c r="I52" s="555"/>
+      <c r="J52" s="555"/>
+      <c r="K52" s="555"/>
+      <c r="L52" s="555"/>
       <c r="M52" s="87"/>
     </row>
     <row r="53" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A53" s="718"/>
-      <c r="B53" s="712"/>
-      <c r="C53" s="712"/>
-      <c r="D53" s="712"/>
-      <c r="E53" s="712"/>
-      <c r="F53" s="712"/>
-      <c r="G53" s="712"/>
-      <c r="H53" s="711"/>
-      <c r="I53" s="711"/>
-      <c r="J53" s="711"/>
-      <c r="K53" s="711"/>
-      <c r="L53" s="711"/>
+      <c r="A53" s="562"/>
+      <c r="B53" s="556"/>
+      <c r="C53" s="556"/>
+      <c r="D53" s="556"/>
+      <c r="E53" s="556"/>
+      <c r="F53" s="556"/>
+      <c r="G53" s="556"/>
+      <c r="H53" s="555"/>
+      <c r="I53" s="555"/>
+      <c r="J53" s="555"/>
+      <c r="K53" s="555"/>
+      <c r="L53" s="555"/>
       <c r="M53" s="87"/>
     </row>
     <row r="54" spans="1:13" ht="6.75" customHeight="1">
-      <c r="A54" s="719"/>
+      <c r="A54" s="563"/>
       <c r="B54" s="460"/>
       <c r="C54" s="460"/>
       <c r="D54" s="460"/>
       <c r="E54" s="460"/>
       <c r="F54" s="460"/>
       <c r="G54" s="460"/>
-      <c r="H54" s="720"/>
+      <c r="H54" s="564"/>
       <c r="I54" s="458"/>
-      <c r="J54" s="721"/>
-      <c r="K54" s="721"/>
-      <c r="L54" s="721"/>
+      <c r="J54" s="565"/>
+      <c r="K54" s="565"/>
+      <c r="L54" s="565"/>
       <c r="M54" s="87"/>
     </row>
     <row r="55" spans="1:13" ht="30" customHeight="1">
-      <c r="A55" s="719"/>
+      <c r="A55" s="563"/>
       <c r="B55" s="460"/>
-      <c r="C55" s="728" t="s">
-        <v>341</v>
-      </c>
-      <c r="D55" s="726"/>
-      <c r="E55" s="730"/>
+      <c r="C55" s="649" t="s">
+        <v>340</v>
+      </c>
+      <c r="D55" s="650"/>
+      <c r="E55" s="651"/>
       <c r="F55" s="460"/>
-      <c r="G55" s="728" t="s">
-        <v>340</v>
-      </c>
-      <c r="H55" s="726"/>
-      <c r="I55" s="726"/>
-      <c r="J55" s="730"/>
+      <c r="G55" s="649" t="s">
+        <v>347</v>
+      </c>
+      <c r="H55" s="650"/>
+      <c r="I55" s="650"/>
+      <c r="J55" s="651"/>
       <c r="K55" s="460"/>
       <c r="L55" s="460"/>
       <c r="M55" s="87"/>
     </row>
     <row r="56" spans="1:13" ht="15.9" customHeight="1">
-      <c r="A56" s="722"/>
+      <c r="A56" s="566"/>
       <c r="B56" s="460"/>
-      <c r="C56" s="729"/>
-      <c r="D56" s="727"/>
-      <c r="E56" s="731"/>
+      <c r="C56" s="652"/>
+      <c r="D56" s="653"/>
+      <c r="E56" s="654"/>
       <c r="F56" s="460"/>
-      <c r="G56" s="729"/>
-      <c r="H56" s="727"/>
-      <c r="I56" s="727"/>
-      <c r="J56" s="731"/>
+      <c r="G56" s="652"/>
+      <c r="H56" s="653"/>
+      <c r="I56" s="653"/>
+      <c r="J56" s="654"/>
       <c r="K56" s="460"/>
       <c r="L56" s="460"/>
       <c r="M56" s="87"/>
     </row>
     <row r="57" spans="1:13" ht="13.2" customHeight="1">
-      <c r="B57" s="637"/>
-      <c r="C57" s="732"/>
-      <c r="D57" s="733"/>
-      <c r="E57" s="734"/>
+      <c r="B57" s="508"/>
+      <c r="C57" s="655"/>
+      <c r="D57" s="656"/>
+      <c r="E57" s="657"/>
       <c r="F57" s="460"/>
-      <c r="G57" s="732"/>
-      <c r="H57" s="733"/>
-      <c r="I57" s="733"/>
-      <c r="J57" s="734"/>
-      <c r="K57" s="638"/>
+      <c r="G57" s="655"/>
+      <c r="H57" s="656"/>
+      <c r="I57" s="656"/>
+      <c r="J57" s="657"/>
+      <c r="K57" s="509"/>
       <c r="L57" s="460"/>
       <c r="M57" s="87"/>
     </row>
     <row r="58" spans="1:13" ht="13.2" customHeight="1">
-      <c r="A58" s="723" t="s">
+      <c r="A58" s="567" t="s">
         <v>91</v>
       </c>
       <c r="B58" s="460"/>
@@ -10376,13 +10441,13 @@
       <c r="M58" s="87"/>
     </row>
     <row r="59" spans="1:13" ht="15.9" customHeight="1">
-      <c r="A59" s="723" t="s">
+      <c r="A59" s="567" t="s">
         <v>334</v>
       </c>
       <c r="B59" s="460"/>
       <c r="C59" s="460"/>
       <c r="D59" s="460"/>
-      <c r="E59" s="724" t="s">
+      <c r="E59" s="568" t="s">
         <v>323</v>
       </c>
       <c r="F59" s="460"/>
@@ -10396,20 +10461,20 @@
     </row>
     <row r="60" spans="1:13" ht="3.75" customHeight="1"/>
     <row r="61" spans="1:13" ht="30.75" customHeight="1">
-      <c r="A61" s="725" t="s">
+      <c r="A61" s="658" t="s">
         <v>324</v>
       </c>
-      <c r="B61" s="725"/>
-      <c r="C61" s="725"/>
-      <c r="D61" s="725"/>
-      <c r="E61" s="725"/>
-      <c r="F61" s="725"/>
-      <c r="G61" s="725"/>
-      <c r="H61" s="725"/>
-      <c r="I61" s="725"/>
-      <c r="J61" s="725"/>
-      <c r="K61" s="725"/>
-      <c r="L61" s="725"/>
+      <c r="B61" s="658"/>
+      <c r="C61" s="658"/>
+      <c r="D61" s="658"/>
+      <c r="E61" s="658"/>
+      <c r="F61" s="658"/>
+      <c r="G61" s="658"/>
+      <c r="H61" s="658"/>
+      <c r="I61" s="658"/>
+      <c r="J61" s="658"/>
+      <c r="K61" s="658"/>
+      <c r="L61" s="658"/>
     </row>
     <row r="62" spans="1:13" ht="15.9" customHeight="1"/>
     <row r="63" spans="1:13" ht="15.9" customHeight="1"/>
@@ -10521,40 +10586,40 @@
       <c r="N1" s="327"/>
     </row>
     <row r="2" spans="1:17" ht="15.9" customHeight="1">
-      <c r="A2" s="491" t="s">
+      <c r="A2" s="572" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="491"/>
-      <c r="C2" s="491"/>
-      <c r="D2" s="491"/>
-      <c r="E2" s="491"/>
-      <c r="F2" s="491"/>
-      <c r="G2" s="491"/>
-      <c r="H2" s="491"/>
-      <c r="I2" s="491"/>
-      <c r="J2" s="491"/>
-      <c r="K2" s="491"/>
-      <c r="L2" s="491"/>
-      <c r="M2" s="491"/>
-      <c r="N2" s="491"/>
+      <c r="B2" s="572"/>
+      <c r="C2" s="572"/>
+      <c r="D2" s="572"/>
+      <c r="E2" s="572"/>
+      <c r="F2" s="572"/>
+      <c r="G2" s="572"/>
+      <c r="H2" s="572"/>
+      <c r="I2" s="572"/>
+      <c r="J2" s="572"/>
+      <c r="K2" s="572"/>
+      <c r="L2" s="572"/>
+      <c r="M2" s="572"/>
+      <c r="N2" s="572"/>
     </row>
     <row r="3" spans="1:17" ht="15.9" customHeight="1">
-      <c r="A3" s="549">
+      <c r="A3" s="668">
         <v>0</v>
       </c>
-      <c r="B3" s="549"/>
-      <c r="C3" s="549"/>
-      <c r="D3" s="549"/>
-      <c r="E3" s="549"/>
-      <c r="F3" s="549"/>
-      <c r="G3" s="549"/>
-      <c r="H3" s="549"/>
-      <c r="I3" s="549"/>
-      <c r="J3" s="549"/>
-      <c r="K3" s="549"/>
-      <c r="L3" s="549"/>
-      <c r="M3" s="549"/>
-      <c r="N3" s="549"/>
+      <c r="B3" s="668"/>
+      <c r="C3" s="668"/>
+      <c r="D3" s="668"/>
+      <c r="E3" s="668"/>
+      <c r="F3" s="668"/>
+      <c r="G3" s="668"/>
+      <c r="H3" s="668"/>
+      <c r="I3" s="668"/>
+      <c r="J3" s="668"/>
+      <c r="K3" s="668"/>
+      <c r="L3" s="668"/>
+      <c r="M3" s="668"/>
+      <c r="N3" s="668"/>
     </row>
     <row r="4" spans="1:17" ht="15.9" customHeight="1"/>
     <row r="5" spans="1:17" ht="15" customHeight="1">
@@ -10594,18 +10659,18 @@
       <c r="B6" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="561">
+      <c r="C6" s="681">
         <f>+Resumen!P3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="561"/>
-      <c r="E6" s="561"/>
-      <c r="F6" s="561"/>
-      <c r="G6" s="561"/>
-      <c r="H6" s="561"/>
-      <c r="I6" s="561"/>
-      <c r="J6" s="561"/>
-      <c r="K6" s="561"/>
+      <c r="D6" s="681"/>
+      <c r="E6" s="681"/>
+      <c r="F6" s="681"/>
+      <c r="G6" s="681"/>
+      <c r="H6" s="681"/>
+      <c r="I6" s="681"/>
+      <c r="J6" s="681"/>
+      <c r="K6" s="681"/>
       <c r="L6" s="488" t="s">
         <v>267</v>
       </c>
@@ -10660,19 +10725,19 @@
       <c r="B8" s="177" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="561">
+      <c r="C8" s="681">
         <f>+Resumen!P5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="561"/>
-      <c r="E8" s="561"/>
-      <c r="F8" s="561"/>
-      <c r="G8" s="561"/>
-      <c r="H8" s="561"/>
-      <c r="I8" s="561"/>
-      <c r="J8" s="561"/>
-      <c r="K8" s="561"/>
-      <c r="L8" s="561"/>
+      <c r="D8" s="681"/>
+      <c r="E8" s="681"/>
+      <c r="F8" s="681"/>
+      <c r="G8" s="681"/>
+      <c r="H8" s="681"/>
+      <c r="I8" s="681"/>
+      <c r="J8" s="681"/>
+      <c r="K8" s="681"/>
+      <c r="L8" s="681"/>
       <c r="M8" s="181"/>
       <c r="N8" s="180"/>
       <c r="O8" s="335"/>
@@ -10701,43 +10766,43 @@
       <c r="Q9" s="335"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="550" t="s">
+      <c r="A10" s="669" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="551"/>
-      <c r="C10" s="551"/>
-      <c r="D10" s="551"/>
-      <c r="E10" s="551"/>
-      <c r="F10" s="551"/>
-      <c r="G10" s="551"/>
-      <c r="H10" s="551"/>
-      <c r="I10" s="551"/>
-      <c r="J10" s="551"/>
-      <c r="K10" s="551"/>
-      <c r="L10" s="551"/>
-      <c r="M10" s="551"/>
-      <c r="N10" s="552"/>
+      <c r="B10" s="670"/>
+      <c r="C10" s="670"/>
+      <c r="D10" s="670"/>
+      <c r="E10" s="670"/>
+      <c r="F10" s="670"/>
+      <c r="G10" s="670"/>
+      <c r="H10" s="670"/>
+      <c r="I10" s="670"/>
+      <c r="J10" s="670"/>
+      <c r="K10" s="670"/>
+      <c r="L10" s="670"/>
+      <c r="M10" s="670"/>
+      <c r="N10" s="671"/>
       <c r="O10" s="335"/>
       <c r="P10" s="335"/>
       <c r="Q10" s="335"/>
     </row>
     <row r="11" spans="1:17" ht="12" customHeight="1">
-      <c r="A11" s="553" t="s">
+      <c r="A11" s="672" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="554"/>
-      <c r="C11" s="554"/>
-      <c r="D11" s="554"/>
-      <c r="E11" s="554"/>
-      <c r="F11" s="554"/>
-      <c r="G11" s="554"/>
-      <c r="H11" s="554"/>
-      <c r="I11" s="554"/>
-      <c r="J11" s="554"/>
-      <c r="K11" s="554"/>
-      <c r="L11" s="554"/>
-      <c r="M11" s="554"/>
-      <c r="N11" s="555"/>
+      <c r="B11" s="673"/>
+      <c r="C11" s="673"/>
+      <c r="D11" s="673"/>
+      <c r="E11" s="673"/>
+      <c r="F11" s="673"/>
+      <c r="G11" s="673"/>
+      <c r="H11" s="673"/>
+      <c r="I11" s="673"/>
+      <c r="J11" s="673"/>
+      <c r="K11" s="673"/>
+      <c r="L11" s="673"/>
+      <c r="M11" s="673"/>
+      <c r="N11" s="674"/>
       <c r="O11" s="335"/>
       <c r="P11" s="335"/>
       <c r="Q11" s="335"/>
@@ -10907,16 +10972,16 @@
       <c r="A18" s="328"/>
       <c r="B18" s="328"/>
       <c r="C18" s="328"/>
-      <c r="D18" s="544"/>
-      <c r="E18" s="544"/>
+      <c r="D18" s="677"/>
+      <c r="E18" s="677"/>
       <c r="F18" s="328"/>
       <c r="G18" s="328"/>
       <c r="H18" s="328"/>
       <c r="I18" s="328"/>
       <c r="J18" s="328"/>
       <c r="K18" s="328"/>
-      <c r="L18" s="544"/>
-      <c r="M18" s="544"/>
+      <c r="L18" s="677"/>
+      <c r="M18" s="677"/>
       <c r="N18" s="328"/>
       <c r="O18" s="335"/>
       <c r="P18" s="335"/>
@@ -10926,14 +10991,14 @@
       <c r="A19" s="328"/>
       <c r="B19" s="328"/>
       <c r="C19" s="328"/>
-      <c r="D19" s="558" t="s">
+      <c r="D19" s="678" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="558"/>
-      <c r="F19" s="558"/>
-      <c r="G19" s="558"/>
-      <c r="H19" s="558"/>
-      <c r="I19" s="558"/>
+      <c r="E19" s="678"/>
+      <c r="F19" s="678"/>
+      <c r="G19" s="678"/>
+      <c r="H19" s="678"/>
+      <c r="I19" s="678"/>
       <c r="J19" s="329" t="s">
         <v>109</v>
       </c>
@@ -10966,8 +11031,8 @@
         <f>+'Datos ensayo'!G17</f>
         <v>1</v>
       </c>
-      <c r="L20" s="556"/>
-      <c r="M20" s="556"/>
+      <c r="L20" s="675"/>
+      <c r="M20" s="675"/>
       <c r="N20" s="330"/>
       <c r="O20" s="335"/>
       <c r="P20" s="335"/>
@@ -10992,8 +11057,8 @@
         <f>+'Datos ensayo'!G18</f>
         <v>0</v>
       </c>
-      <c r="L21" s="556"/>
-      <c r="M21" s="556"/>
+      <c r="L21" s="675"/>
+      <c r="M21" s="675"/>
       <c r="N21" s="330"/>
       <c r="O21" s="335"/>
       <c r="P21" s="335"/>
@@ -11018,8 +11083,8 @@
         <f>+'Datos ensayo'!H19</f>
         <v>0.00</v>
       </c>
-      <c r="L22" s="557"/>
-      <c r="M22" s="557"/>
+      <c r="L22" s="676"/>
+      <c r="M22" s="676"/>
       <c r="N22" s="331"/>
       <c r="O22" s="341"/>
       <c r="P22" s="341"/>
@@ -11368,11 +11433,11 @@
       <c r="H37" s="195"/>
       <c r="I37" s="197"/>
       <c r="J37" s="197"/>
-      <c r="K37" s="560">
+      <c r="K37" s="680">
         <f>+Resumen!E27</f>
         <v>0</v>
       </c>
-      <c r="L37" s="560"/>
+      <c r="L37" s="680"/>
       <c r="M37" s="159"/>
       <c r="N37" s="159"/>
       <c r="O37" s="335"/>
@@ -11392,11 +11457,11 @@
       <c r="H38" s="195"/>
       <c r="I38" s="197"/>
       <c r="J38" s="197"/>
-      <c r="K38" s="559">
+      <c r="K38" s="679">
         <f>+Resumen!E28</f>
         <v>0</v>
       </c>
-      <c r="L38" s="559"/>
+      <c r="L38" s="679"/>
       <c r="M38" s="159"/>
       <c r="N38" s="159"/>
       <c r="O38" s="335"/>
@@ -11463,22 +11528,22 @@
       <c r="Q42" s="335"/>
     </row>
     <row r="43" spans="1:17" ht="24" customHeight="1">
-      <c r="A43" s="546" t="s">
+      <c r="A43" s="665" t="s">
         <v>127</v>
       </c>
-      <c r="B43" s="546"/>
-      <c r="C43" s="546"/>
-      <c r="D43" s="548"/>
-      <c r="E43" s="548"/>
-      <c r="F43" s="548"/>
-      <c r="G43" s="548"/>
-      <c r="H43" s="548"/>
-      <c r="I43" s="548"/>
-      <c r="J43" s="548"/>
-      <c r="K43" s="548"/>
-      <c r="L43" s="548"/>
-      <c r="M43" s="548"/>
-      <c r="N43" s="548"/>
+      <c r="B43" s="665"/>
+      <c r="C43" s="665"/>
+      <c r="D43" s="667"/>
+      <c r="E43" s="667"/>
+      <c r="F43" s="667"/>
+      <c r="G43" s="667"/>
+      <c r="H43" s="667"/>
+      <c r="I43" s="667"/>
+      <c r="J43" s="667"/>
+      <c r="K43" s="667"/>
+      <c r="L43" s="667"/>
+      <c r="M43" s="667"/>
+      <c r="N43" s="667"/>
       <c r="O43" s="335"/>
       <c r="P43" s="335"/>
       <c r="Q43" s="335"/>
@@ -11494,22 +11559,22 @@
       <c r="Q44" s="335"/>
     </row>
     <row r="45" spans="1:17" ht="23.25" customHeight="1">
-      <c r="A45" s="546" t="s">
+      <c r="A45" s="665" t="s">
         <v>266</v>
       </c>
-      <c r="B45" s="546"/>
-      <c r="C45" s="546"/>
-      <c r="D45" s="546"/>
-      <c r="E45" s="546"/>
-      <c r="F45" s="546"/>
-      <c r="G45" s="546"/>
-      <c r="H45" s="546"/>
-      <c r="I45" s="546"/>
-      <c r="J45" s="546"/>
-      <c r="K45" s="546"/>
-      <c r="L45" s="546"/>
-      <c r="M45" s="546"/>
-      <c r="N45" s="546"/>
+      <c r="B45" s="665"/>
+      <c r="C45" s="665"/>
+      <c r="D45" s="665"/>
+      <c r="E45" s="665"/>
+      <c r="F45" s="665"/>
+      <c r="G45" s="665"/>
+      <c r="H45" s="665"/>
+      <c r="I45" s="665"/>
+      <c r="J45" s="665"/>
+      <c r="K45" s="665"/>
+      <c r="L45" s="665"/>
+      <c r="M45" s="665"/>
+      <c r="N45" s="665"/>
       <c r="O45" s="335"/>
       <c r="P45" s="335"/>
       <c r="Q45" s="335"/>
@@ -11547,10 +11612,10 @@
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
-      <c r="K48" s="545"/>
-      <c r="L48" s="545"/>
-      <c r="M48" s="545"/>
-      <c r="N48" s="545"/>
+      <c r="K48" s="664"/>
+      <c r="L48" s="664"/>
+      <c r="M48" s="664"/>
+      <c r="N48" s="664"/>
       <c r="O48" s="335"/>
       <c r="P48" s="335"/>
       <c r="Q48" s="335"/>
@@ -11572,10 +11637,10 @@
       <c r="A50" s="199"/>
       <c r="B50" s="199"/>
       <c r="C50" s="199"/>
-      <c r="K50" s="545"/>
-      <c r="L50" s="545"/>
-      <c r="M50" s="545"/>
-      <c r="N50" s="545"/>
+      <c r="K50" s="664"/>
+      <c r="L50" s="664"/>
+      <c r="M50" s="664"/>
+      <c r="N50" s="664"/>
       <c r="O50" s="335"/>
       <c r="P50" s="335"/>
       <c r="Q50" s="335"/>
@@ -11593,10 +11658,10 @@
       <c r="H51" s="342"/>
       <c r="I51" s="342"/>
       <c r="J51" s="342"/>
-      <c r="K51" s="545"/>
-      <c r="L51" s="545"/>
-      <c r="M51" s="545"/>
-      <c r="N51" s="545"/>
+      <c r="K51" s="664"/>
+      <c r="L51" s="664"/>
+      <c r="M51" s="664"/>
+      <c r="N51" s="664"/>
     </row>
     <row r="52" spans="1:17" ht="11.25" customHeight="1">
       <c r="A52" s="197" t="s">
@@ -11611,12 +11676,12 @@
       <c r="H52" s="342"/>
       <c r="I52" s="342"/>
       <c r="J52" s="342"/>
-      <c r="K52" s="545" t="s">
+      <c r="K52" s="664" t="s">
         <v>129</v>
       </c>
-      <c r="L52" s="545"/>
-      <c r="M52" s="545"/>
-      <c r="N52" s="545"/>
+      <c r="L52" s="664"/>
+      <c r="M52" s="664"/>
+      <c r="N52" s="664"/>
     </row>
     <row r="53" spans="1:17" ht="15.9" customHeight="1">
       <c r="M53" s="187"/>
@@ -11666,20 +11731,20 @@
       <c r="N58" s="189"/>
     </row>
     <row r="59" spans="1:17" ht="30" customHeight="1">
-      <c r="A59" s="548"/>
-      <c r="B59" s="548"/>
-      <c r="C59" s="548"/>
-      <c r="D59" s="548"/>
-      <c r="E59" s="548"/>
-      <c r="F59" s="548"/>
-      <c r="G59" s="548"/>
-      <c r="H59" s="548"/>
-      <c r="I59" s="548"/>
-      <c r="J59" s="548"/>
-      <c r="K59" s="548"/>
-      <c r="L59" s="548"/>
-      <c r="M59" s="548"/>
-      <c r="N59" s="548"/>
+      <c r="A59" s="667"/>
+      <c r="B59" s="667"/>
+      <c r="C59" s="667"/>
+      <c r="D59" s="667"/>
+      <c r="E59" s="667"/>
+      <c r="F59" s="667"/>
+      <c r="G59" s="667"/>
+      <c r="H59" s="667"/>
+      <c r="I59" s="667"/>
+      <c r="J59" s="667"/>
+      <c r="K59" s="667"/>
+      <c r="L59" s="667"/>
+      <c r="M59" s="667"/>
+      <c r="N59" s="667"/>
     </row>
     <row r="60" spans="1:17" ht="30" customHeight="1">
       <c r="A60" s="195"/>
@@ -11698,20 +11763,20 @@
       <c r="N60" s="342"/>
     </row>
     <row r="61" spans="1:17" ht="39.75" customHeight="1">
-      <c r="A61" s="548"/>
-      <c r="B61" s="548"/>
-      <c r="C61" s="548"/>
-      <c r="D61" s="548"/>
-      <c r="E61" s="548"/>
-      <c r="F61" s="548"/>
-      <c r="G61" s="548"/>
-      <c r="H61" s="548"/>
-      <c r="I61" s="548"/>
-      <c r="J61" s="548"/>
-      <c r="K61" s="548"/>
-      <c r="L61" s="548"/>
-      <c r="M61" s="548"/>
-      <c r="N61" s="548"/>
+      <c r="A61" s="667"/>
+      <c r="B61" s="667"/>
+      <c r="C61" s="667"/>
+      <c r="D61" s="667"/>
+      <c r="E61" s="667"/>
+      <c r="F61" s="667"/>
+      <c r="G61" s="667"/>
+      <c r="H61" s="667"/>
+      <c r="I61" s="667"/>
+      <c r="J61" s="667"/>
+      <c r="K61" s="667"/>
+      <c r="L61" s="667"/>
+      <c r="M61" s="667"/>
+      <c r="N61" s="667"/>
     </row>
     <row r="62" spans="1:17" ht="30" customHeight="1">
       <c r="A62" s="196"/>
@@ -11800,15 +11865,15 @@
       <c r="N78" s="335"/>
     </row>
     <row r="79" spans="11:14">
-      <c r="K79" s="547"/>
-      <c r="L79" s="547"/>
-      <c r="M79" s="547"/>
+      <c r="K79" s="666"/>
+      <c r="L79" s="666"/>
+      <c r="M79" s="666"/>
       <c r="N79" s="335"/>
     </row>
     <row r="80" spans="11:14">
-      <c r="K80" s="547"/>
-      <c r="L80" s="547"/>
-      <c r="M80" s="547"/>
+      <c r="K80" s="666"/>
+      <c r="L80" s="666"/>
+      <c r="M80" s="666"/>
       <c r="N80" s="335"/>
     </row>
     <row r="81" spans="1:14">
@@ -12021,35 +12086,35 @@
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
       <c r="A2" s="407"/>
-      <c r="B2" s="562" t="s">
+      <c r="B2" s="682" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="562"/>
-      <c r="D2" s="562"/>
-      <c r="E2" s="562"/>
-      <c r="F2" s="562"/>
-      <c r="G2" s="562"/>
-      <c r="H2" s="562"/>
-      <c r="I2" s="562"/>
-      <c r="J2" s="562"/>
-      <c r="K2" s="562"/>
+      <c r="C2" s="682"/>
+      <c r="D2" s="682"/>
+      <c r="E2" s="682"/>
+      <c r="F2" s="682"/>
+      <c r="G2" s="682"/>
+      <c r="H2" s="682"/>
+      <c r="I2" s="682"/>
+      <c r="J2" s="682"/>
+      <c r="K2" s="682"/>
       <c r="L2" s="394"/>
       <c r="M2" s="406"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="407"/>
-      <c r="B3" s="562" t="s">
+      <c r="B3" s="682" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="562"/>
-      <c r="D3" s="562"/>
-      <c r="E3" s="562"/>
-      <c r="F3" s="562"/>
-      <c r="G3" s="562"/>
-      <c r="H3" s="562"/>
-      <c r="I3" s="562"/>
-      <c r="J3" s="562"/>
-      <c r="K3" s="562"/>
+      <c r="C3" s="682"/>
+      <c r="D3" s="682"/>
+      <c r="E3" s="682"/>
+      <c r="F3" s="682"/>
+      <c r="G3" s="682"/>
+      <c r="H3" s="682"/>
+      <c r="I3" s="682"/>
+      <c r="J3" s="682"/>
+      <c r="K3" s="682"/>
       <c r="L3" s="394"/>
       <c r="M3" s="406"/>
     </row>
@@ -12070,12 +12135,12 @@
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="407"/>
-      <c r="B5" s="568" t="s">
+      <c r="B5" s="688" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="569"/>
-      <c r="D5" s="569"/>
-      <c r="E5" s="570"/>
+      <c r="C5" s="689"/>
+      <c r="D5" s="689"/>
+      <c r="E5" s="690"/>
       <c r="F5" s="349">
         <f>+Resumen!J26</f>
         <v>0</v>
@@ -12110,12 +12175,12 @@
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="407"/>
-      <c r="B7" s="568" t="s">
+      <c r="B7" s="688" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="569"/>
-      <c r="D7" s="569"/>
-      <c r="E7" s="570"/>
+      <c r="C7" s="689"/>
+      <c r="D7" s="689"/>
+      <c r="E7" s="690"/>
       <c r="F7" s="349">
         <f>+IF(F5="A",0.1,0.01)</f>
         <v>0.01</v>
@@ -12265,19 +12330,19 @@
       <c r="A17" s="416">
         <v>1</v>
       </c>
-      <c r="B17" s="571" t="s">
+      <c r="B17" s="691" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="572"/>
-      <c r="D17" s="572"/>
-      <c r="E17" s="573"/>
+      <c r="C17" s="692"/>
+      <c r="D17" s="692"/>
+      <c r="E17" s="693"/>
       <c r="F17" s="417" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="451">
         <v>1</v>
       </c>
-      <c r="H17" s="564" t="s">
+      <c r="H17" s="684" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -12292,12 +12357,12 @@
       <c r="A18" s="416">
         <v>2</v>
       </c>
-      <c r="B18" s="571" t="s">
+      <c r="B18" s="691" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="572"/>
-      <c r="D18" s="572"/>
-      <c r="E18" s="573"/>
+      <c r="C18" s="692"/>
+      <c r="D18" s="692"/>
+      <c r="E18" s="693"/>
       <c r="F18" s="417" t="s">
         <v>36</v>
       </c>
@@ -12305,7 +12370,7 @@
         <f>+Resumen!I32</f>
         <v>0</v>
       </c>
-      <c r="H18" s="564"/>
+      <c r="H18" s="684"/>
       <c r="J18" s="4" t="s">
         <v>276</v>
       </c>
@@ -12318,12 +12383,12 @@
       <c r="A19" s="416">
         <v>3</v>
       </c>
-      <c r="B19" s="571" t="s">
+      <c r="B19" s="691" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="572"/>
-      <c r="D19" s="572"/>
-      <c r="E19" s="573"/>
+      <c r="C19" s="692"/>
+      <c r="D19" s="692"/>
+      <c r="E19" s="693"/>
       <c r="F19" s="417" t="s">
         <v>41</v>
       </c>
@@ -12347,12 +12412,12 @@
       <c r="A20" s="416">
         <v>4</v>
       </c>
-      <c r="B20" s="571" t="s">
+      <c r="B20" s="691" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="572"/>
-      <c r="D20" s="572"/>
-      <c r="E20" s="573"/>
+      <c r="C20" s="692"/>
+      <c r="D20" s="692"/>
+      <c r="E20" s="693"/>
       <c r="F20" s="417" t="s">
         <v>41</v>
       </c>
@@ -12405,12 +12470,12 @@
       <c r="A22" s="416">
         <v>6</v>
       </c>
-      <c r="B22" s="571" t="s">
+      <c r="B22" s="691" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="572"/>
-      <c r="D22" s="572"/>
-      <c r="E22" s="573"/>
+      <c r="C22" s="692"/>
+      <c r="D22" s="692"/>
+      <c r="E22" s="693"/>
       <c r="F22" s="419" t="s">
         <v>41</v>
       </c>
@@ -12434,12 +12499,12 @@
       <c r="A23" s="416">
         <v>7</v>
       </c>
-      <c r="B23" s="571" t="s">
+      <c r="B23" s="691" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="572"/>
-      <c r="D23" s="572"/>
-      <c r="E23" s="573"/>
+      <c r="C23" s="692"/>
+      <c r="D23" s="692"/>
+      <c r="E23" s="693"/>
       <c r="F23" s="417" t="s">
         <v>41</v>
       </c>
@@ -12463,12 +12528,12 @@
       <c r="A24" s="416">
         <v>8</v>
       </c>
-      <c r="B24" s="571" t="s">
+      <c r="B24" s="691" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="572"/>
-      <c r="D24" s="572"/>
-      <c r="E24" s="573"/>
+      <c r="C24" s="692"/>
+      <c r="D24" s="692"/>
+      <c r="E24" s="693"/>
       <c r="F24" s="419" t="s">
         <v>41</v>
       </c>
@@ -12492,12 +12557,12 @@
       <c r="A25" s="416">
         <v>9</v>
       </c>
-      <c r="B25" s="574" t="s">
+      <c r="B25" s="694" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="575"/>
-      <c r="D25" s="575"/>
-      <c r="E25" s="576"/>
+      <c r="C25" s="695"/>
+      <c r="D25" s="695"/>
+      <c r="E25" s="696"/>
       <c r="F25" s="419" t="s">
         <v>56</v>
       </c>
@@ -12613,24 +12678,24 @@
     </row>
     <row r="31" spans="1:12" ht="15.9" customHeight="1">
       <c r="A31" s="407"/>
-      <c r="B31" s="563" t="s">
+      <c r="B31" s="683" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="563"/>
-      <c r="D31" s="563"/>
-      <c r="E31" s="563"/>
-      <c r="F31" s="563"/>
-      <c r="G31" s="563"/>
+      <c r="C31" s="683"/>
+      <c r="D31" s="683"/>
+      <c r="E31" s="683"/>
+      <c r="F31" s="683"/>
+      <c r="G31" s="683"/>
       <c r="L31" s="414"/>
     </row>
     <row r="32" spans="1:12" ht="26.25" customHeight="1">
       <c r="A32" s="407"/>
-      <c r="B32" s="568" t="s">
+      <c r="B32" s="688" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="569"/>
-      <c r="D32" s="569"/>
-      <c r="E32" s="570"/>
+      <c r="C32" s="689"/>
+      <c r="D32" s="689"/>
+      <c r="E32" s="690"/>
       <c r="F32" s="389" t="s">
         <v>143</v>
       </c>
@@ -12641,12 +12706,12 @@
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
       <c r="A33" s="407"/>
-      <c r="B33" s="565" t="s">
+      <c r="B33" s="685" t="s">
         <v>145</v>
       </c>
-      <c r="C33" s="566"/>
-      <c r="D33" s="566"/>
-      <c r="E33" s="567"/>
+      <c r="C33" s="686"/>
+      <c r="D33" s="686"/>
+      <c r="E33" s="687"/>
       <c r="F33" s="348" t="s">
         <v>146</v>
       </c>
@@ -12657,12 +12722,12 @@
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
       <c r="A34" s="407"/>
-      <c r="B34" s="565" t="s">
+      <c r="B34" s="685" t="s">
         <v>147</v>
       </c>
-      <c r="C34" s="566"/>
-      <c r="D34" s="566"/>
-      <c r="E34" s="567"/>
+      <c r="C34" s="686"/>
+      <c r="D34" s="686"/>
+      <c r="E34" s="687"/>
       <c r="F34" s="348" t="s">
         <v>148</v>
       </c>
@@ -12673,12 +12738,12 @@
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1">
       <c r="A35" s="407"/>
-      <c r="B35" s="565" t="s">
+      <c r="B35" s="685" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="566"/>
-      <c r="D35" s="566"/>
-      <c r="E35" s="567"/>
+      <c r="C35" s="686"/>
+      <c r="D35" s="686"/>
+      <c r="E35" s="687"/>
       <c r="F35" s="348" t="s">
         <v>150</v>
       </c>
@@ -12689,24 +12754,24 @@
     </row>
     <row r="36" spans="1:12" ht="16.5" customHeight="1">
       <c r="A36" s="407"/>
-      <c r="B36" s="563" t="s">
+      <c r="B36" s="683" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="563"/>
-      <c r="D36" s="563"/>
-      <c r="E36" s="563"/>
-      <c r="F36" s="563"/>
-      <c r="G36" s="563"/>
+      <c r="C36" s="683"/>
+      <c r="D36" s="683"/>
+      <c r="E36" s="683"/>
+      <c r="F36" s="683"/>
+      <c r="G36" s="683"/>
       <c r="L36" s="414"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1">
       <c r="A37" s="407"/>
-      <c r="B37" s="565" t="s">
+      <c r="B37" s="685" t="s">
         <v>257</v>
       </c>
-      <c r="C37" s="566"/>
-      <c r="D37" s="566"/>
-      <c r="E37" s="567"/>
+      <c r="C37" s="686"/>
+      <c r="D37" s="686"/>
+      <c r="E37" s="687"/>
       <c r="F37" s="348" t="s">
         <v>152</v>
       </c>
@@ -12717,12 +12782,12 @@
     </row>
     <row r="38" spans="1:12" ht="16.5" customHeight="1">
       <c r="A38" s="407"/>
-      <c r="B38" s="565" t="s">
+      <c r="B38" s="685" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="566"/>
-      <c r="D38" s="566"/>
-      <c r="E38" s="567"/>
+      <c r="C38" s="686"/>
+      <c r="D38" s="686"/>
+      <c r="E38" s="687"/>
       <c r="F38" s="348" t="s">
         <v>154</v>
       </c>
@@ -12733,12 +12798,12 @@
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
       <c r="A39" s="407"/>
-      <c r="B39" s="565" t="s">
+      <c r="B39" s="685" t="s">
         <v>155</v>
       </c>
-      <c r="C39" s="566"/>
-      <c r="D39" s="566"/>
-      <c r="E39" s="567"/>
+      <c r="C39" s="686"/>
+      <c r="D39" s="686"/>
+      <c r="E39" s="687"/>
       <c r="F39" s="348" t="s">
         <v>156</v>
       </c>
@@ -12903,7 +12968,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="21.88671875" style="357" customWidth="1"/>
@@ -12920,16 +12985,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A1" s="586"/>
-      <c r="B1" s="587"/>
-      <c r="C1" s="577" t="s">
+      <c r="A1" s="713"/>
+      <c r="B1" s="714"/>
+      <c r="C1" s="704" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="578"/>
-      <c r="E1" s="578"/>
-      <c r="F1" s="578"/>
-      <c r="G1" s="578"/>
-      <c r="H1" s="579"/>
+      <c r="D1" s="705"/>
+      <c r="E1" s="705"/>
+      <c r="F1" s="705"/>
+      <c r="G1" s="705"/>
+      <c r="H1" s="706"/>
       <c r="I1" s="227" t="s">
         <v>158</v>
       </c>
@@ -12938,14 +13003,14 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A2" s="588"/>
-      <c r="B2" s="589"/>
-      <c r="C2" s="580"/>
-      <c r="D2" s="581"/>
-      <c r="E2" s="581"/>
-      <c r="F2" s="581"/>
-      <c r="G2" s="581"/>
-      <c r="H2" s="582"/>
+      <c r="A2" s="715"/>
+      <c r="B2" s="716"/>
+      <c r="C2" s="707"/>
+      <c r="D2" s="708"/>
+      <c r="E2" s="708"/>
+      <c r="F2" s="708"/>
+      <c r="G2" s="708"/>
+      <c r="H2" s="709"/>
       <c r="I2" s="227" t="s">
         <v>160</v>
       </c>
@@ -12954,14 +13019,14 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A3" s="588"/>
-      <c r="B3" s="589"/>
-      <c r="C3" s="580"/>
-      <c r="D3" s="581"/>
-      <c r="E3" s="581"/>
-      <c r="F3" s="581"/>
-      <c r="G3" s="581"/>
-      <c r="H3" s="582"/>
+      <c r="A3" s="715"/>
+      <c r="B3" s="716"/>
+      <c r="C3" s="707"/>
+      <c r="D3" s="708"/>
+      <c r="E3" s="708"/>
+      <c r="F3" s="708"/>
+      <c r="G3" s="708"/>
+      <c r="H3" s="709"/>
       <c r="I3" s="227" t="s">
         <v>161</v>
       </c>
@@ -12970,14 +13035,14 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A4" s="590"/>
-      <c r="B4" s="591"/>
-      <c r="C4" s="583"/>
-      <c r="D4" s="584"/>
-      <c r="E4" s="584"/>
-      <c r="F4" s="584"/>
-      <c r="G4" s="584"/>
-      <c r="H4" s="585"/>
+      <c r="A4" s="717"/>
+      <c r="B4" s="718"/>
+      <c r="C4" s="710"/>
+      <c r="D4" s="711"/>
+      <c r="E4" s="711"/>
+      <c r="F4" s="711"/>
+      <c r="G4" s="711"/>
+      <c r="H4" s="712"/>
       <c r="I4" s="227" t="s">
         <v>162</v>
       </c>
@@ -13158,16 +13223,16 @@
       <c r="J39" s="355"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A40" s="596" t="s">
+      <c r="A40" s="723" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="597"/>
-      <c r="C40" s="597"/>
-      <c r="D40" s="597"/>
-      <c r="E40" s="597"/>
-      <c r="F40" s="597"/>
-      <c r="G40" s="597"/>
-      <c r="H40" s="598"/>
+      <c r="B40" s="724"/>
+      <c r="C40" s="724"/>
+      <c r="D40" s="724"/>
+      <c r="E40" s="724"/>
+      <c r="F40" s="724"/>
+      <c r="G40" s="724"/>
+      <c r="H40" s="725"/>
       <c r="I40" s="355"/>
       <c r="J40" s="355"/>
     </row>
@@ -13601,42 +13666,42 @@
       <c r="J55" s="355"/>
     </row>
     <row r="56" spans="1:10" s="361" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A56" s="599" t="s">
+      <c r="A56" s="726" t="s">
         <v>204</v>
       </c>
-      <c r="B56" s="600"/>
-      <c r="C56" s="601"/>
+      <c r="B56" s="727"/>
+      <c r="C56" s="728"/>
       <c r="D56" s="287" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="288"/>
-      <c r="F56" s="592" t="e">
+      <c r="F56" s="719" t="e">
         <f>SQRT((H43*H43)+(H47*H47)+(H51*H51)+(H55*H55))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G56" s="592"/>
-      <c r="H56" s="593"/>
+      <c r="G56" s="719"/>
+      <c r="H56" s="720"/>
       <c r="I56" s="355" t="s">
         <v>205</v>
       </c>
       <c r="J56" s="355"/>
     </row>
     <row r="57" spans="1:10" s="361" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A57" s="602" t="s">
+      <c r="A57" s="729" t="s">
         <v>206</v>
       </c>
-      <c r="B57" s="603"/>
-      <c r="C57" s="604"/>
+      <c r="B57" s="730"/>
+      <c r="C57" s="731"/>
       <c r="D57" s="325" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="289"/>
-      <c r="F57" s="594" t="e">
+      <c r="F57" s="721" t="e">
         <f>F56*2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G57" s="594"/>
-      <c r="H57" s="595"/>
+      <c r="G57" s="721"/>
+      <c r="H57" s="722"/>
       <c r="I57" s="355" t="s">
         <v>207</v>
       </c>
@@ -13805,9 +13870,43 @@
     <row r="69" spans="1:10" ht="15" customHeight="1"/>
     <row r="70" spans="1:10" ht="15" customHeight="1"/>
     <row r="71" spans="1:10" ht="15" customHeight="1"/>
+    <row r="72" spans="1:10">
+      <c r="A72" s="569" t="s">
+        <v>341</v>
+      </c>
+      <c r="B72" s="697" t="s">
+        <v>342</v>
+      </c>
+      <c r="C72" s="698"/>
+      <c r="D72" s="570"/>
+      <c r="E72" s="699" t="s">
+        <v>343</v>
+      </c>
+      <c r="F72" s="700"/>
+      <c r="G72" s="701" t="s">
+        <v>344</v>
+      </c>
+      <c r="H72" s="698"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="D73" s="570"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="571" t="s">
+        <v>345</v>
+      </c>
+      <c r="B74" s="702"/>
+      <c r="C74" s="698"/>
+      <c r="D74" s="570"/>
+      <c r="E74" s="703" t="s">
+        <v>346</v>
+      </c>
+      <c r="F74" s="700"/>
+      <c r="G74" s="702"/>
+      <c r="H74" s="698"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pycoBIIXBRq0lZ5QzQV7agIPVEFMKREq32NU/vGsNmnBDF5r4AhDUeZ6HUrCSJZE/s+GK4awCDp58+2UHke7tA==" saltValue="b+2DODrb2DHlNuGRAuelXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="7">
+  <mergeCells count="13">
     <mergeCell ref="C1:H4"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="F56:H56"/>
@@ -13815,6 +13914,12 @@
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A57:C57"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G74:H74"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -15243,22 +15348,22 @@
       </c>
     </row>
     <row r="47" spans="2:15">
-      <c r="C47" s="605" t="s">
+      <c r="C47" s="732" t="s">
         <v>219</v>
       </c>
-      <c r="D47" s="605"/>
-      <c r="E47" s="605"/>
-      <c r="F47" s="605"/>
-      <c r="G47" s="605"/>
-      <c r="H47" s="605"/>
-      <c r="J47" s="607" t="s">
+      <c r="D47" s="732"/>
+      <c r="E47" s="732"/>
+      <c r="F47" s="732"/>
+      <c r="G47" s="732"/>
+      <c r="H47" s="732"/>
+      <c r="J47" s="734" t="s">
         <v>219</v>
       </c>
-      <c r="K47" s="608"/>
-      <c r="L47" s="608"/>
-      <c r="M47" s="608"/>
-      <c r="N47" s="608"/>
-      <c r="O47" s="609"/>
+      <c r="K47" s="735"/>
+      <c r="L47" s="735"/>
+      <c r="M47" s="735"/>
+      <c r="N47" s="735"/>
+      <c r="O47" s="736"/>
     </row>
     <row r="48" spans="2:15">
       <c r="C48" s="219"/>
@@ -15268,9 +15373,9 @@
       <c r="G48" s="220"/>
       <c r="H48" s="221"/>
       <c r="J48" s="270"/>
-      <c r="K48" s="606"/>
-      <c r="L48" s="606"/>
-      <c r="M48" s="606"/>
+      <c r="K48" s="733"/>
+      <c r="L48" s="733"/>
+      <c r="M48" s="733"/>
       <c r="N48" s="220"/>
       <c r="O48" s="221"/>
     </row>
@@ -15534,7 +15639,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B8" s="614" t="s">
+      <c r="B8" s="741" t="s">
         <v>225</v>
       </c>
       <c r="C8" s="443">
@@ -15551,7 +15656,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B9" s="614"/>
+      <c r="B9" s="741"/>
       <c r="C9" s="443">
         <v>9.3000000000000007</v>
       </c>
@@ -15566,7 +15671,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B10" s="614"/>
+      <c r="B10" s="741"/>
       <c r="C10" s="443">
         <v>9.34</v>
       </c>
@@ -15581,7 +15686,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B11" s="614"/>
+      <c r="B11" s="741"/>
       <c r="C11" s="443">
         <v>9.4600000000000009</v>
       </c>
@@ -15596,7 +15701,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B12" s="614"/>
+      <c r="B12" s="741"/>
       <c r="C12" s="443">
         <v>9.3800000000000008</v>
       </c>
@@ -15611,7 +15716,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B13" s="614"/>
+      <c r="B13" s="741"/>
       <c r="C13" s="443">
         <v>9.35</v>
       </c>
@@ -15626,42 +15731,42 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B14" s="614"/>
+      <c r="B14" s="741"/>
       <c r="C14" s="369"/>
       <c r="D14" s="369"/>
       <c r="E14" s="316"/>
       <c r="F14" s="316"/>
     </row>
     <row r="15" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B15" s="614"/>
+      <c r="B15" s="741"/>
       <c r="C15" s="369"/>
       <c r="D15" s="369"/>
       <c r="E15" s="316"/>
       <c r="F15" s="316"/>
     </row>
     <row r="16" spans="2:6" ht="16.5" customHeight="1">
-      <c r="B16" s="614"/>
+      <c r="B16" s="741"/>
       <c r="C16" s="369"/>
       <c r="D16" s="369"/>
       <c r="E16" s="316"/>
       <c r="F16" s="316"/>
     </row>
     <row r="17" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B17" s="614"/>
+      <c r="B17" s="741"/>
       <c r="C17" s="369"/>
       <c r="D17" s="369"/>
       <c r="E17" s="316"/>
       <c r="F17" s="316"/>
     </row>
     <row r="18" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B18" s="614"/>
+      <c r="B18" s="741"/>
       <c r="C18" s="317"/>
       <c r="D18" s="317"/>
       <c r="E18" s="316"/>
       <c r="F18" s="316"/>
     </row>
     <row r="19" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B19" s="614"/>
+      <c r="B19" s="741"/>
       <c r="C19" s="317"/>
       <c r="D19" s="317"/>
       <c r="E19" s="316"/>
@@ -15800,120 +15905,120 @@
       <c r="B28" s="297" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="615">
+      <c r="C28" s="742">
         <f>+C23*C24+D23*D24+E23*E24+F23*F24</f>
         <v>225.69</v>
       </c>
-      <c r="D28" s="615"/>
-      <c r="E28" s="615"/>
+      <c r="D28" s="742"/>
+      <c r="E28" s="742"/>
       <c r="F28" s="298"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="297" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="616">
+      <c r="C29" s="743">
         <f>+C23*POWER(C24,2)+F23*POWER(F24,2)+E23*POWER(E24,2)+D23*POWER(D24,2)</f>
         <v>2122.3448833333332</v>
       </c>
-      <c r="D29" s="616"/>
-      <c r="E29" s="616"/>
+      <c r="D29" s="743"/>
+      <c r="E29" s="743"/>
       <c r="F29" s="298"/>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="297" t="s">
         <v>234</v>
       </c>
-      <c r="C30" s="616">
+      <c r="C30" s="743">
         <f>+SUM(C23:F23)</f>
         <v>24</v>
       </c>
-      <c r="D30" s="616"/>
-      <c r="E30" s="616"/>
+      <c r="D30" s="743"/>
+      <c r="E30" s="743"/>
       <c r="F30" s="298"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="297" t="s">
         <v>235</v>
       </c>
-      <c r="C31" s="616">
+      <c r="C31" s="743">
         <f>+POWER(C23,2)+POWER(F23,2)+POWER(E23,2)+POWER(D23,2)</f>
         <v>144</v>
       </c>
-      <c r="D31" s="616"/>
-      <c r="E31" s="616"/>
+      <c r="D31" s="743"/>
+      <c r="E31" s="743"/>
       <c r="F31" s="298"/>
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="297" t="s">
         <v>236</v>
       </c>
-      <c r="C32" s="613">
+      <c r="C32" s="740">
         <f>(C20-1)*SUM(C26:F26)</f>
         <v>5.4616666666666855E-2</v>
       </c>
-      <c r="D32" s="613"/>
-      <c r="E32" s="613"/>
+      <c r="D32" s="740"/>
+      <c r="E32" s="740"/>
       <c r="F32" s="298"/>
     </row>
     <row r="33" spans="2:6" ht="15" customHeight="1">
       <c r="B33" s="293" t="s">
         <v>237</v>
       </c>
-      <c r="C33" s="610">
+      <c r="C33" s="737">
         <f>ABS((C32/(C30-C21)))</f>
         <v>2.7308333333333429E-3</v>
       </c>
-      <c r="D33" s="610"/>
-      <c r="E33" s="610"/>
+      <c r="D33" s="737"/>
+      <c r="E33" s="737"/>
       <c r="F33" s="298"/>
     </row>
     <row r="34" spans="2:6" ht="15" customHeight="1">
       <c r="B34" s="293" t="s">
         <v>238</v>
       </c>
-      <c r="C34" s="611">
+      <c r="C34" s="738">
         <f>ABS((((C29*C30-(C28^2))/(C30*(C21-1)))-(C33))*((C30*(C21-1))/((C30^2)-C31)))</f>
         <v>2.4185185184478981E-4</v>
       </c>
-      <c r="D34" s="611"/>
-      <c r="E34" s="611"/>
+      <c r="D34" s="738"/>
+      <c r="E34" s="738"/>
       <c r="F34" s="298"/>
     </row>
     <row r="35" spans="2:6" ht="15" customHeight="1">
       <c r="B35" s="293" t="s">
         <v>239</v>
       </c>
-      <c r="C35" s="612">
+      <c r="C35" s="739">
         <f>(C33+C34)/1000000</f>
         <v>2.9726851851781329E-9</v>
       </c>
-      <c r="D35" s="612"/>
-      <c r="E35" s="612"/>
+      <c r="D35" s="739"/>
+      <c r="E35" s="739"/>
       <c r="F35" s="298"/>
     </row>
     <row r="36" spans="2:6" ht="15" customHeight="1">
       <c r="B36" s="293" t="s">
         <v>240</v>
       </c>
-      <c r="C36" s="612">
+      <c r="C36" s="739">
         <f>SQRT(C33)</f>
         <v>5.2257375874926432E-2</v>
       </c>
-      <c r="D36" s="612"/>
-      <c r="E36" s="612"/>
+      <c r="D36" s="739"/>
+      <c r="E36" s="739"/>
       <c r="F36" s="298"/>
     </row>
     <row r="37" spans="2:6" ht="15" customHeight="1">
       <c r="B37" s="293" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="612">
+      <c r="C37" s="739">
         <f>+SQRT(C33+C34)</f>
         <v>5.4522336571153414E-2</v>
       </c>
-      <c r="D37" s="612"/>
-      <c r="E37" s="612"/>
+      <c r="D37" s="739"/>
+      <c r="E37" s="739"/>
       <c r="F37" s="298"/>
     </row>
     <row r="38" spans="2:6" ht="15" customHeight="1"/>
@@ -15956,10 +16061,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A2" s="617" t="s">
+      <c r="A2" s="744" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="617"/>
+      <c r="B2" s="744"/>
       <c r="C2" s="5" t="s">
         <v>243</v>
       </c>
